--- a/policy.xlsx
+++ b/policy.xlsx
@@ -126,6 +126,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -150,13 +151,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
@@ -439,6 +441,7 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -480,6 +483,7 @@
       <c r="M2" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -521,6 +525,7 @@
       <c r="M3" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -562,6 +567,7 @@
       <c r="M4" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -603,6 +609,7 @@
       <c r="M5" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -644,6 +651,7 @@
       <c r="M6" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -685,6 +693,7 @@
       <c r="M7" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
@@ -726,6 +735,7 @@
       <c r="M8" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
@@ -767,6 +777,7 @@
       <c r="M9" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
@@ -808,6 +819,7 @@
       <c r="M10" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
@@ -849,6 +861,7 @@
       <c r="M11" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
@@ -890,6 +903,7 @@
       <c r="M12" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
@@ -931,6 +945,7 @@
       <c r="M13" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
@@ -972,6 +987,7 @@
       <c r="M14" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
@@ -1013,6 +1029,7 @@
       <c r="M15" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
@@ -1054,6 +1071,7 @@
       <c r="M16" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
@@ -1095,6 +1113,7 @@
       <c r="M17" s="1">
         <v>50000.0</v>
       </c>
+      <c r="N17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
@@ -1136,6 +1155,7 @@
       <c r="M18" s="1">
         <v>0.0</v>
       </c>
+      <c r="N18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
@@ -1177,6 +1197,7 @@
       <c r="M19" s="1">
         <v>100000.0</v>
       </c>
+      <c r="N19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
@@ -1218,6 +1239,7 @@
       <c r="M20" s="1">
         <v>100000.0</v>
       </c>
+      <c r="N20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
@@ -1259,6 +1281,119 @@
       <c r="M21" s="1">
         <v>30000.0</v>
       </c>
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1277,1619 +1412,1619 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3">
+      <c r="B1" s="4">
         <v>19800.0</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="4">
         <v>24000.0</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="4">
         <v>33000.0</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="4">
         <v>37000.0</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="4">
         <v>41000.0</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="4">
         <v>42000.0</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="4">
         <v>44000.0</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="4">
         <v>45000.0</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="4">
         <v>47000.0</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="4">
         <v>49000.0</v>
       </c>
-      <c r="L1" s="3">
+      <c r="L1" s="4">
         <v>50000.0</v>
       </c>
-      <c r="M1" s="3">
+      <c r="M1" s="4">
         <v>55000.0</v>
       </c>
-      <c r="N1" s="3">
+      <c r="N1" s="4">
         <v>58000.0</v>
       </c>
-      <c r="O1" s="3">
+      <c r="O1" s="4">
         <v>61000.0</v>
       </c>
-      <c r="P1" s="3">
+      <c r="P1" s="4">
         <v>63000.0</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="Q1" s="4">
         <v>65000.0</v>
       </c>
-      <c r="R1" s="3">
+      <c r="R1" s="4">
         <v>67000.0</v>
       </c>
-      <c r="S1" s="3">
+      <c r="S1" s="4">
         <v>69000.0</v>
       </c>
-      <c r="T1" s="3">
+      <c r="T1" s="4">
         <v>77000.0</v>
       </c>
-      <c r="U1" s="3">
+      <c r="U1" s="4">
         <v>80000.0</v>
       </c>
-      <c r="V1" s="3">
+      <c r="V1" s="4">
         <v>90000.0</v>
       </c>
-      <c r="W1" s="3">
+      <c r="W1" s="4">
         <v>100000.0</v>
       </c>
-      <c r="X1" s="3">
+      <c r="X1" s="4">
         <v>110000.0</v>
       </c>
-      <c r="Y1" s="3">
+      <c r="Y1" s="4">
         <v>130000.0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="N2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="O2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="S2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="U2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="V2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="X2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Y2" s="3">
+      <c r="B2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Y2" s="4">
         <v>0.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="N3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="O3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="R3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="S3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="U3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="V3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="X3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Y3" s="3">
+      <c r="B3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="S3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="T3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="U3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Y3" s="4">
         <v>0.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="N4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="O4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="R4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="S4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="U4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="V4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="X4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Y4" s="3">
+      <c r="B4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="S4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="T4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="U4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="V4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="W4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="X4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Y4" s="4">
         <v>0.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>115000.0</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="4">
         <v>133000.0</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <v>210000.0</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <v>228000.0</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="4">
         <v>228000.0</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V5" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="W5" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X5" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y5" s="3">
+      <c r="V5" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="W5" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X5" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y5" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>115000.0</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="4">
         <v>133000.0</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="4">
         <v>210000.0</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <v>228000.0</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <v>228000.0</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T6" s="3">
+      <c r="T6" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U6" s="3">
+      <c r="U6" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V6" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="W6" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X6" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y6" s="3">
+      <c r="V6" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="W6" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X6" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y6" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>115000.0</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="4">
         <v>133000.0</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="4">
         <v>210000.0</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <v>228000.0</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="4">
         <v>228000.0</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R7" s="3">
+      <c r="R7" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S7" s="3">
+      <c r="S7" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T7" s="3">
+      <c r="T7" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U7" s="3">
+      <c r="U7" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V7" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="W7" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X7" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y7" s="3">
+      <c r="V7" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="W7" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X7" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y7" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>115000.0</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="4">
         <v>133000.0</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="4">
         <v>210000.0</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <v>228000.0</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="4">
         <v>228000.0</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T8" s="3">
+      <c r="T8" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U8" s="3">
+      <c r="U8" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V8" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="W8" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X8" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="V8" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="W8" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X8" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y8" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>115000.0</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="4">
         <v>133000.0</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="4">
         <v>210000.0</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="4">
         <v>228000.0</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="4">
         <v>228000.0</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V9" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="W9" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X9" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="V9" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="W9" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X9" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y9" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>115000.0</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <v>133000.0</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="4">
         <v>210000.0</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <v>228000.0</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="4">
         <v>228000.0</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T10" s="3">
+      <c r="T10" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V10" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="W10" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X10" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="V10" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="W10" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X10" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y10" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>36000.0</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="4">
         <v>42000.0</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="4">
         <v>60000.0</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="4">
         <v>69000.0</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="4">
         <v>75000.0</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="4">
         <v>77000.0</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="4">
         <v>78000.0</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="4">
         <v>85000.0</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="4">
         <v>86000.0</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="4">
         <v>89000.0</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="4">
         <v>91000.0</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="4">
         <v>100000.0</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="4">
         <v>107000.0</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11" s="4">
         <v>111000.0</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="4">
         <v>116000.0</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="4">
         <v>119000.0</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="4">
         <v>122000.0</v>
       </c>
-      <c r="S11" s="3">
+      <c r="S11" s="4">
         <v>127000.0</v>
       </c>
-      <c r="T11" s="3">
+      <c r="T11" s="4">
         <v>139000.0</v>
       </c>
-      <c r="U11" s="3">
+      <c r="U11" s="4">
         <v>147000.0</v>
       </c>
-      <c r="V11" s="3">
+      <c r="V11" s="4">
         <v>150000.0</v>
       </c>
-      <c r="W11" s="3">
+      <c r="W11" s="4">
         <v>183000.0</v>
       </c>
-      <c r="X11" s="3">
+      <c r="X11" s="4">
         <v>201000.0</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="Y11" s="4">
         <v>250000.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>36000.0</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="4">
         <v>42000.0</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="4">
         <v>60000.0</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="4">
         <v>69000.0</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <v>75000.0</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="4">
         <v>77000.0</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="4">
         <v>78000.0</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="4">
         <v>85000.0</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="4">
         <v>86000.0</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="4">
         <v>89000.0</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="4">
         <v>91000.0</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="4">
         <v>100000.0</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="4">
         <v>107000.0</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="4">
         <v>111000.0</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="4">
         <v>116000.0</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="4">
         <v>119000.0</v>
       </c>
-      <c r="R12" s="3">
+      <c r="R12" s="4">
         <v>122000.0</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="4">
         <v>127000.0</v>
       </c>
-      <c r="T12" s="3">
+      <c r="T12" s="4">
         <v>139000.0</v>
       </c>
-      <c r="U12" s="3">
+      <c r="U12" s="4">
         <v>147000.0</v>
       </c>
-      <c r="V12" s="3">
+      <c r="V12" s="4">
         <v>150000.0</v>
       </c>
-      <c r="W12" s="3">
+      <c r="W12" s="4">
         <v>183000.0</v>
       </c>
-      <c r="X12" s="3">
+      <c r="X12" s="4">
         <v>201000.0</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Y12" s="4">
         <v>250000.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>36000.0</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="4">
         <v>42000.0</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="4">
         <v>60000.0</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="4">
         <v>69000.0</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="4">
         <v>75000.0</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="4">
         <v>77000.0</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="4">
         <v>78000.0</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="4">
         <v>85000.0</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="4">
         <v>86000.0</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="4">
         <v>89000.0</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="4">
         <v>91000.0</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="4">
         <v>100000.0</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="4">
         <v>107000.0</v>
       </c>
-      <c r="O13" s="3">
+      <c r="O13" s="4">
         <v>111000.0</v>
       </c>
-      <c r="P13" s="3">
+      <c r="P13" s="4">
         <v>116000.0</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="Q13" s="4">
         <v>119000.0</v>
       </c>
-      <c r="R13" s="3">
+      <c r="R13" s="4">
         <v>122000.0</v>
       </c>
-      <c r="S13" s="3">
+      <c r="S13" s="4">
         <v>127000.0</v>
       </c>
-      <c r="T13" s="3">
+      <c r="T13" s="4">
         <v>139000.0</v>
       </c>
-      <c r="U13" s="3">
+      <c r="U13" s="4">
         <v>147000.0</v>
       </c>
-      <c r="V13" s="3">
+      <c r="V13" s="4">
         <v>150000.0</v>
       </c>
-      <c r="W13" s="3">
+      <c r="W13" s="4">
         <v>183000.0</v>
       </c>
-      <c r="X13" s="3">
+      <c r="X13" s="4">
         <v>201000.0</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="Y13" s="4">
         <v>250000.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>157000.0</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="4">
         <v>181000.0</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <v>246000.0</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="4">
         <v>281000.0</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="4">
         <v>305000.0</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="4">
         <v>311000.0</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="4">
         <v>317000.0</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="4">
         <v>341000.0</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="4">
         <v>347000.0</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="4">
         <v>358000.0</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="4">
         <v>364000.0</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="4">
         <v>400000.0</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="4">
         <v>423000.0</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="4">
         <v>441000.0</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="4">
         <v>459000.0</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="4">
         <v>471000.0</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="4">
         <v>482000.0</v>
       </c>
-      <c r="S14" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="S14" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="T14" s="4">
         <v>547000.0</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="4">
         <v>600000.0</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="4">
         <v>700000.0</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="4">
         <v>700000.0</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="4">
         <v>700000.0</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="4">
         <v>700000.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>115000.0</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="4">
         <v>133000.0</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="4">
         <v>210000.0</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="4">
         <v>228000.0</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R15" s="3">
+      <c r="R15" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S15" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="T15" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="U15" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="V15" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="W15" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X15" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="S15" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="T15" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="U15" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="V15" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="W15" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X15" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y15" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>115000.0</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="4">
         <v>133000.0</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="4">
         <v>210000.0</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="4">
         <v>228000.0</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M16" s="3">
+      <c r="M16" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O16" s="3">
+      <c r="O16" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P16" s="3">
+      <c r="P16" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="Q16" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R16" s="3">
+      <c r="R16" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S16" s="3">
+      <c r="S16" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T16" s="3">
+      <c r="T16" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U16" s="3">
+      <c r="U16" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V16" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="W16" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X16" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y16" s="3">
+      <c r="V16" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="W16" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X16" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y16" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>115000.0</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="4">
         <v>133000.0</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="4">
         <v>210000.0</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="4">
         <v>228000.0</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="4">
         <v>228000.0</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S17" s="3">
+      <c r="S17" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T17" s="3">
+      <c r="T17" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U17" s="3">
+      <c r="U17" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V17" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="W17" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X17" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="V17" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="W17" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X17" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y17" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>55000.0</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="4">
         <v>82000.0</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="4">
         <v>156000.0</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="4">
         <v>196000.0</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="4">
         <v>223000.0</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="4">
         <v>230000.0</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="4">
         <v>236000.0</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="4">
         <v>263000.0</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="4">
         <v>270000.0</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="4">
         <v>283000.0</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="4">
         <v>290000.0</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="4">
         <v>330000.0</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="4">
         <v>357000.0</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="4">
         <v>377000.0</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="4">
         <v>398000.0</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="4">
         <v>411000.0</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="4">
         <v>425000.0</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="4">
         <v>445000.0</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="4">
         <v>498000.0</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="4">
         <v>530000.0</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="4">
         <v>600000.0</v>
       </c>
-      <c r="W18" s="3">
+      <c r="W18" s="4">
         <v>600000.0</v>
       </c>
-      <c r="X18" s="3">
+      <c r="X18" s="4">
         <v>600000.0</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="4">
         <v>600000.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="O19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="R19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="S19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="U19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="V19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="X19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Y19" s="3">
+      <c r="B19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="P19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="R19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="S19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="T19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="U19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="V19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="W19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="X19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Y19" s="4">
         <v>0.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>36000.0</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="4">
         <v>42000.0</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="4">
         <v>60000.0</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="4">
         <v>69000.0</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="4">
         <v>75000.0</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="4">
         <v>77000.0</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="4">
         <v>78000.0</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="4">
         <v>85000.0</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="4">
         <v>86000.0</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="4">
         <v>89000.0</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="4">
         <v>91000.0</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="4">
         <v>100000.0</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="4">
         <v>107000.0</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="4">
         <v>111000.0</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="4">
         <v>116000.0</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="4">
         <v>119000.0</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="4">
         <v>122000.0</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="4">
         <v>127000.0</v>
       </c>
-      <c r="T20" s="3">
+      <c r="T20" s="4">
         <v>137000.0</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="4">
         <v>147000.0</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="4">
         <v>150000.0</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W20" s="4">
         <v>183000.0</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X20" s="4">
         <v>201000.0</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="4">
         <v>250000.0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>36000.0</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="4">
         <v>42000.0</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="4">
         <v>60000.0</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="4">
         <v>69000.0</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="4">
         <v>75000.0</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="4">
         <v>77000.0</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="4">
         <v>78000.0</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="4">
         <v>85000.0</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="4">
         <v>86000.0</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="4">
         <v>89000.0</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="4">
         <v>91000.0</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="4">
         <v>100000.0</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="4">
         <v>107000.0</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="4">
         <v>111000.0</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="4">
         <v>116000.0</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="4">
         <v>119000.0</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="4">
         <v>122000.0</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="4">
         <v>127000.0</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="4">
         <v>139000.0</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="4">
         <v>147000.0</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="4">
         <v>150000.0</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="4">
         <v>183000.0</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="4">
         <v>201000.0</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="4">
         <v>250000.0</v>
       </c>
     </row>
@@ -2910,1745 +3045,1745 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3">
+      <c r="B1" s="4">
         <v>22000.0</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="4">
         <v>28000.0</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="4">
         <v>29000.0</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="4">
         <v>33000.0</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="4">
         <v>37000.0</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="4">
         <v>39000.0</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="4">
         <v>43000.0</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="4">
         <v>44000.0</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="4">
         <v>45000.0</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="4">
         <v>47000.0</v>
       </c>
-      <c r="L1" s="3">
+      <c r="L1" s="4">
         <v>49000.0</v>
       </c>
-      <c r="M1" s="3">
+      <c r="M1" s="4">
         <v>55000.0</v>
       </c>
-      <c r="N1" s="3">
+      <c r="N1" s="4">
         <v>59000.0</v>
       </c>
-      <c r="O1" s="3">
+      <c r="O1" s="4">
         <v>61000.0</v>
       </c>
-      <c r="P1" s="3">
+      <c r="P1" s="4">
         <v>63000.0</v>
       </c>
-      <c r="Q1" s="3">
+      <c r="Q1" s="4">
         <v>66000.0</v>
       </c>
-      <c r="R1" s="3">
+      <c r="R1" s="4">
         <v>68000.0</v>
       </c>
-      <c r="S1" s="3">
+      <c r="S1" s="4">
         <v>69000.0</v>
       </c>
-      <c r="T1" s="3">
+      <c r="T1" s="4">
         <v>70000.0</v>
       </c>
-      <c r="U1" s="3">
+      <c r="U1" s="4">
         <v>75000.0</v>
       </c>
-      <c r="V1" s="3">
+      <c r="V1" s="4">
         <v>78000.0</v>
       </c>
-      <c r="W1" s="3">
+      <c r="W1" s="4">
         <v>85000.0</v>
       </c>
-      <c r="X1" s="3">
+      <c r="X1" s="4">
         <v>95000.0</v>
       </c>
-      <c r="Y1" s="3">
+      <c r="Y1" s="4">
         <v>105000.0</v>
       </c>
-      <c r="Z1" s="3">
+      <c r="Z1" s="4">
         <v>115000.0</v>
       </c>
-      <c r="AA1" s="3">
+      <c r="AA1" s="4">
         <v>130000.0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="N2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="O2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="R2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="S2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="U2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="V2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="X2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AA2" s="3">
+      <c r="B2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="AA2" s="4">
         <v>0.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="N3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="O3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="R3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="S3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="U3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="V3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="X3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Y3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Z3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AA3" s="3">
+      <c r="B3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="S3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="T3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="U3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Z3" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="AA3" s="4">
         <v>0.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="N4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="O4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="R4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="S4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="U4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="V4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="X4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AA4" s="3">
+      <c r="B4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="R4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="S4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="T4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="U4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="V4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="W4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="X4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Y4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Z4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="AA4" s="4">
         <v>0.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D5" s="3">
+      <c r="B5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D5" s="4">
         <v>175000.0</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="4">
         <v>198000.0</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="4">
         <v>222000.0</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="4">
         <v>257000.0</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="4">
         <v>262000.0</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="4">
         <v>268000.0</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="4">
         <v>280000.0</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="4">
         <v>291000.0</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="4">
         <v>326000.0</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="4">
         <v>350000.0</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="4">
         <v>361000.0</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="4">
         <v>373000.0</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="4">
         <v>390000.0</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="4">
         <v>402000.0</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="4">
         <v>407000.0</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5" s="4">
         <v>414000.0</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="4">
         <v>442000.0</v>
       </c>
-      <c r="V5" s="3">
+      <c r="V5" s="4">
         <v>460000.0</v>
       </c>
-      <c r="W5" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X5" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y5" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Z5" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="AA5" s="3">
+      <c r="W5" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X5" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z5" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="AA5" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="B6" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D6" s="4">
         <v>175000.0</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="4">
         <v>198000.0</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <v>222000.0</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="4">
         <v>257000.0</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="4">
         <v>262000.0</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="4">
         <v>268000.0</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="4">
         <v>280000.0</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="4">
         <v>291000.0</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="4">
         <v>326000.0</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="4">
         <v>350000.0</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="4">
         <v>361000.0</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="4">
         <v>373000.0</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="4">
         <v>390000.0</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="4">
         <v>402000.0</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="4">
         <v>407000.0</v>
       </c>
-      <c r="T6" s="3">
+      <c r="T6" s="4">
         <v>414000.0</v>
       </c>
-      <c r="U6" s="3">
+      <c r="U6" s="4">
         <v>442000.0</v>
       </c>
-      <c r="V6" s="3">
+      <c r="V6" s="4">
         <v>460000.0</v>
       </c>
-      <c r="W6" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X6" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="AA6" s="3">
+      <c r="W6" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X6" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y6" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z6" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="AA6" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="B7" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D7" s="4">
         <v>175000.0</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="4">
         <v>198000.0</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <v>222000.0</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="4">
         <v>257000.0</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="4">
         <v>262000.0</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="4">
         <v>268000.0</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="4">
         <v>280000.0</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="4">
         <v>291000.0</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="4">
         <v>326000.0</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="4">
         <v>350000.0</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7" s="4">
         <v>361000.0</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="4">
         <v>373000.0</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="4">
         <v>390000.0</v>
       </c>
-      <c r="R7" s="3">
+      <c r="R7" s="4">
         <v>402000.0</v>
       </c>
-      <c r="S7" s="3">
+      <c r="S7" s="4">
         <v>407000.0</v>
       </c>
-      <c r="T7" s="3">
+      <c r="T7" s="4">
         <v>414000.0</v>
       </c>
-      <c r="U7" s="3">
+      <c r="U7" s="4">
         <v>442000.0</v>
       </c>
-      <c r="V7" s="3">
+      <c r="V7" s="4">
         <v>460000.0</v>
       </c>
-      <c r="W7" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X7" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="AA7" s="3">
+      <c r="W7" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X7" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="AA7" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="B8" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D8" s="4">
         <v>175000.0</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="4">
         <v>198000.0</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <v>222000.0</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="4">
         <v>257000.0</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="4">
         <v>262000.0</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="4">
         <v>268000.0</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="4">
         <v>280000.0</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="4">
         <v>291000.0</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="4">
         <v>326000.0</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="4">
         <v>350000.0</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="4">
         <v>361000.0</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="4">
         <v>373000.0</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="4">
         <v>390000.0</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="4">
         <v>402000.0</v>
       </c>
-      <c r="S8" s="3">
+      <c r="S8" s="4">
         <v>407000.0</v>
       </c>
-      <c r="T8" s="3">
+      <c r="T8" s="4">
         <v>414000.0</v>
       </c>
-      <c r="U8" s="3">
+      <c r="U8" s="4">
         <v>442000.0</v>
       </c>
-      <c r="V8" s="3">
+      <c r="V8" s="4">
         <v>460000.0</v>
       </c>
-      <c r="W8" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X8" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="W8" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X8" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y8" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z8" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="AA8" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="B9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D9" s="4">
         <v>175000.0</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="4">
         <v>198000.0</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="4">
         <v>222000.0</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="4">
         <v>257000.0</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="4">
         <v>262000.0</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="4">
         <v>268000.0</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="4">
         <v>280000.0</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="4">
         <v>291000.0</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="4">
         <v>326000.0</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="4">
         <v>350000.0</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="4">
         <v>361000.0</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="4">
         <v>373000.0</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="4">
         <v>390000.0</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="4">
         <v>402000.0</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="4">
         <v>407000.0</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="4">
         <v>414000.0</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="4">
         <v>442000.0</v>
       </c>
-      <c r="V9" s="3">
+      <c r="V9" s="4">
         <v>460000.0</v>
       </c>
-      <c r="W9" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X9" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="AA9" s="3">
+      <c r="W9" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X9" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="AA9" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="B10" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D10" s="4">
         <v>175000.0</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="4">
         <v>198000.0</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <v>222000.0</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="4">
         <v>257000.0</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="4">
         <v>262000.0</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="4">
         <v>268000.0</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="4">
         <v>280000.0</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="4">
         <v>291000.0</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="4">
         <v>326000.0</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="4">
         <v>350000.0</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="4">
         <v>361000.0</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="4">
         <v>373000.0</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="4">
         <v>390000.0</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="4">
         <v>402000.0</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="4">
         <v>407000.0</v>
       </c>
-      <c r="T10" s="3">
+      <c r="T10" s="4">
         <v>414000.0</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="4">
         <v>442000.0</v>
       </c>
-      <c r="V10" s="3">
+      <c r="V10" s="4">
         <v>460000.0</v>
       </c>
-      <c r="W10" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X10" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="AA10" s="3">
+      <c r="W10" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X10" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z10" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="AA10" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="B11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="4">
         <v>52000.0</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="4">
         <v>59000.0</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="4">
         <v>66000.0</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="4">
         <v>69000.0</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="4">
         <v>76000.0</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="4">
         <v>78000.0</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="4">
         <v>80000.0</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="4">
         <v>84000.0</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="4">
         <v>87000.0</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="4">
         <v>98000.0</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="4">
         <v>105000.0</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11" s="4">
         <v>108000.0</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="4">
         <v>112000.0</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="4">
         <v>117000.0</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="4">
         <v>121000.0</v>
       </c>
-      <c r="S11" s="3">
+      <c r="S11" s="4">
         <v>122000.0</v>
       </c>
-      <c r="T11" s="3">
+      <c r="T11" s="4">
         <v>124000.0</v>
       </c>
-      <c r="U11" s="3">
+      <c r="U11" s="4">
         <v>133000.0</v>
       </c>
-      <c r="V11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W11" s="3">
+      <c r="V11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="W11" s="4">
         <v>151000.0</v>
       </c>
-      <c r="X11" s="3">
+      <c r="X11" s="4">
         <v>168000.0</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="Y11" s="4">
         <v>186000.0</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="Z11" s="4">
         <v>204000.0</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AA11" s="4">
         <v>230000.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="B12" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D12" s="4">
         <v>52000.0</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="4">
         <v>59000.0</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="4">
         <v>66000.0</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="4">
         <v>69000.0</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="4">
         <v>76000.0</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="4">
         <v>78000.0</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="4">
         <v>80000.0</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="4">
         <v>84000.0</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="4">
         <v>87000.0</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="4">
         <v>98000.0</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="4">
         <v>105000.0</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="4">
         <v>108000.0</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="4">
         <v>112000.0</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="4">
         <v>117000.0</v>
       </c>
-      <c r="R12" s="3">
+      <c r="R12" s="4">
         <v>121000.0</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="4">
         <v>122000.0</v>
       </c>
-      <c r="T12" s="3">
+      <c r="T12" s="4">
         <v>124000.0</v>
       </c>
-      <c r="U12" s="3">
+      <c r="U12" s="4">
         <v>133000.0</v>
       </c>
-      <c r="V12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W12" s="3">
+      <c r="V12" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="W12" s="4">
         <v>151000.0</v>
       </c>
-      <c r="X12" s="3">
+      <c r="X12" s="4">
         <v>168000.0</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Y12" s="4">
         <v>186000.0</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="Z12" s="4">
         <v>204000.0</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AA12" s="4">
         <v>230000.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C13" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="B13" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D13" s="4">
         <v>52000.0</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="4">
         <v>59000.0</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="4">
         <v>66000.0</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="4">
         <v>69000.0</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="4">
         <v>76000.0</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="4">
         <v>78000.0</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="4">
         <v>80000.0</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="4">
         <v>84000.0</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="4">
         <v>87000.0</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="4">
         <v>98000.0</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="4">
         <v>105000.0</v>
       </c>
-      <c r="O13" s="3">
+      <c r="O13" s="4">
         <v>108000.0</v>
       </c>
-      <c r="P13" s="3">
+      <c r="P13" s="4">
         <v>112000.0</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="Q13" s="4">
         <v>117000.0</v>
       </c>
-      <c r="R13" s="3">
+      <c r="R13" s="4">
         <v>121000.0</v>
       </c>
-      <c r="S13" s="3">
+      <c r="S13" s="4">
         <v>122000.0</v>
       </c>
-      <c r="T13" s="3">
+      <c r="T13" s="4">
         <v>124000.0</v>
       </c>
-      <c r="U13" s="3">
+      <c r="U13" s="4">
         <v>133000.0</v>
       </c>
-      <c r="V13" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W13" s="3">
+      <c r="V13" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="W13" s="4">
         <v>151000.0</v>
       </c>
-      <c r="X13" s="3">
+      <c r="X13" s="4">
         <v>168000.0</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="Y13" s="4">
         <v>186000.0</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="Z13" s="4">
         <v>204000.0</v>
       </c>
-      <c r="AA13" s="3">
+      <c r="AA13" s="4">
         <v>230000.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C14" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="B14" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D14" s="4">
         <v>239000.0</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="4">
         <v>272000.0</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="4">
         <v>305000.0</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="4">
         <v>322000.0</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="4">
         <v>355000.0</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="4">
         <v>363000.0</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="4">
         <v>371000.0</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="4">
         <v>388000.0</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="4">
         <v>404000.0</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="4">
         <v>454000.0</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="4">
         <v>487000.0</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="4">
         <v>503000.0</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="4">
         <v>519000.0</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="4">
         <v>544000.0</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="4">
         <v>560000.0</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="4">
         <v>569000.0</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="4">
         <v>577000.0</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="4">
         <v>618000.0</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="4">
         <v>700000.0</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="4">
         <v>700000.0</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="4">
         <v>700000.0</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="4">
         <v>700000.0</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="4">
         <v>700000.0</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="4">
         <v>700000.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C15" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="B15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D15" s="4">
         <v>175000.0</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="4">
         <v>198000.0</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="4">
         <v>222000.0</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="4">
         <v>257000.0</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="4">
         <v>262000.0</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="4">
         <v>268000.0</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="4">
         <v>280000.0</v>
       </c>
-      <c r="L15" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="L15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M15" s="4">
         <v>326000.0</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="4">
         <v>350000.0</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="4">
         <v>361000.0</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="4">
         <v>373000.0</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="4">
         <v>390000.0</v>
       </c>
-      <c r="R15" s="3">
+      <c r="R15" s="4">
         <v>402000.0</v>
       </c>
-      <c r="S15" s="3">
+      <c r="S15" s="4">
         <v>407000.0</v>
       </c>
-      <c r="T15" s="3">
+      <c r="T15" s="4">
         <v>414000.0</v>
       </c>
-      <c r="U15" s="3">
+      <c r="U15" s="4">
         <v>442000.0</v>
       </c>
-      <c r="V15" s="3">
+      <c r="V15" s="4">
         <v>460000.0</v>
       </c>
-      <c r="W15" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X15" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="AA15" s="3">
+      <c r="W15" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X15" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z15" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="AA15" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C16" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D16" s="3">
+      <c r="B16" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D16" s="4">
         <v>175000.0</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="4">
         <v>198000.0</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="4">
         <v>222000.0</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="4">
         <v>257000.0</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="4">
         <v>262000.0</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="4">
         <v>268000.0</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="4">
         <v>280000.0</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="4">
         <v>291000.0</v>
       </c>
-      <c r="M16" s="3">
+      <c r="M16" s="4">
         <v>326000.0</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="4">
         <v>350000.0</v>
       </c>
-      <c r="O16" s="3">
+      <c r="O16" s="4">
         <v>361000.0</v>
       </c>
-      <c r="P16" s="3">
+      <c r="P16" s="4">
         <v>373000.0</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="Q16" s="4">
         <v>390000.0</v>
       </c>
-      <c r="R16" s="3">
+      <c r="R16" s="4">
         <v>402000.0</v>
       </c>
-      <c r="S16" s="3">
+      <c r="S16" s="4">
         <v>407000.0</v>
       </c>
-      <c r="T16" s="3">
+      <c r="T16" s="4">
         <v>414000.0</v>
       </c>
-      <c r="U16" s="3">
+      <c r="U16" s="4">
         <v>442000.0</v>
       </c>
-      <c r="V16" s="3">
+      <c r="V16" s="4">
         <v>460000.0</v>
       </c>
-      <c r="W16" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X16" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y16" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Z16" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="AA16" s="3">
+      <c r="W16" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X16" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y16" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z16" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="AA16" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C17" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D17" s="3">
+      <c r="B17" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D17" s="4">
         <v>175000.0</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="4">
         <v>198000.0</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="4">
         <v>222000.0</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="4">
         <v>257000.0</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="4">
         <v>262000.0</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="4">
         <v>268000.0</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="4">
         <v>288000.0</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="4">
         <v>291000.0</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="4">
         <v>326000.0</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="4">
         <v>350000.0</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="4">
         <v>361000.0</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="4">
         <v>373000.0</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="4">
         <v>390000.0</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17" s="4">
         <v>402000.0</v>
       </c>
-      <c r="S17" s="3">
+      <c r="S17" s="4">
         <v>407000.0</v>
       </c>
-      <c r="T17" s="3">
+      <c r="T17" s="4">
         <v>414000.0</v>
       </c>
-      <c r="U17" s="3">
+      <c r="U17" s="4">
         <v>442000.0</v>
       </c>
-      <c r="V17" s="3">
+      <c r="V17" s="4">
         <v>460000.0</v>
       </c>
-      <c r="W17" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X17" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="W17" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X17" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y17" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="AA17" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C18" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D18" s="3">
+      <c r="B18" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C18" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D18" s="4">
         <v>175000.0</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="4">
         <v>198000.0</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="4">
         <v>222000.0</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="4">
         <v>257000.0</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="4">
         <v>262000.0</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="4">
         <v>268000.0</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="4">
         <v>280000.0</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="4">
         <v>291000.0</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="4">
         <v>326000.0</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="4">
         <v>350000.0</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="4">
         <v>361000.0</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="4">
         <v>373000.0</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="4">
         <v>390000.0</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="4">
         <v>402000.0</v>
       </c>
-      <c r="S18" s="3">
+      <c r="S18" s="4">
         <v>407000.0</v>
       </c>
-      <c r="T18" s="3">
+      <c r="T18" s="4">
         <v>414000.0</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="4">
         <v>442000.0</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="4">
         <v>460000.0</v>
       </c>
-      <c r="W18" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="X18" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>500000.0</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="W18" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="X18" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Y18" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z18" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="AA18" s="4">
         <v>500000.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="O19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="R19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="S19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="U19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="V19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="X19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Y19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Z19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AA19" s="3">
+      <c r="B19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="P19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="R19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="S19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="T19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="U19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="V19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="W19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="X19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Y19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="Z19" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="AA19" s="4">
         <v>0.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C20" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D20" s="3">
+      <c r="B20" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C20" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D20" s="4">
         <v>52000.0</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="4">
         <v>59000.0</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="4">
         <v>66000.0</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="4">
         <v>69000.0</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="4">
         <v>76000.0</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="4">
         <v>78000.0</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="4">
         <v>80000.0</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="4">
         <v>84000.0</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="4">
         <v>87000.0</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="4">
         <v>98000.0</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="4">
         <v>105000.0</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="4">
         <v>108000.0</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="4">
         <v>112000.0</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="4">
         <v>117000.0</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="4">
         <v>121000.0</v>
       </c>
-      <c r="S20" s="3">
+      <c r="S20" s="4">
         <v>122000.0</v>
       </c>
-      <c r="T20" s="3">
+      <c r="T20" s="4">
         <v>124000.0</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="4">
         <v>133000.0</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="4">
         <v>138000.0</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W20" s="4">
         <v>151000.0</v>
       </c>
-      <c r="X20" s="3">
+      <c r="X20" s="4">
         <v>168000.0</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="4">
         <v>186000.0</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="4">
         <v>204000.0</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AA20" s="4">
         <v>230000.0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>124000.0</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="4">
         <v>139000.0</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="4">
         <v>141000.0</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="4">
         <v>151000.0</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="4">
         <v>161000.0</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="4">
         <v>277000.0</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="4">
         <v>298000.0</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="4">
         <v>303000.0</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="4">
         <v>308000.0</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="L21" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="L21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="N21" s="3">
+      <c r="M21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O21" s="3">
+      <c r="N21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="P21" s="3">
+      <c r="O21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="P21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="R21" s="3">
+      <c r="Q21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="S21" s="3">
+      <c r="R21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="T21" s="3">
+      <c r="S21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="U21" s="3">
+      <c r="T21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="V21" s="3">
+      <c r="U21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="W21" s="3">
+      <c r="V21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="X21" s="3">
+      <c r="W21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="X21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Y21" s="4">
         <v>319000.0</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="Z21" s="4">
+        <v>319000.0</v>
+      </c>
+      <c r="AA21" s="4">
         <v>319000.0</v>
       </c>
     </row>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -1408,7 +1408,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.25"/>
-    <col customWidth="1" min="2" max="25" width="7.13"/>
+    <col customWidth="1" min="2" max="26" width="7.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1422,69 +1422,72 @@
         <v>24000.0</v>
       </c>
       <c r="D1" s="4">
+        <v>28900.0</v>
+      </c>
+      <c r="E1" s="4">
         <v>33000.0</v>
       </c>
-      <c r="E1" s="4">
+      <c r="F1" s="4">
         <v>37000.0</v>
       </c>
-      <c r="F1" s="4">
+      <c r="G1" s="4">
         <v>41000.0</v>
       </c>
-      <c r="G1" s="4">
+      <c r="H1" s="4">
         <v>42000.0</v>
       </c>
-      <c r="H1" s="4">
+      <c r="I1" s="4">
         <v>44000.0</v>
       </c>
-      <c r="I1" s="4">
+      <c r="J1" s="4">
         <v>45000.0</v>
       </c>
-      <c r="J1" s="4">
+      <c r="K1" s="4">
         <v>47000.0</v>
       </c>
-      <c r="K1" s="4">
+      <c r="L1" s="4">
         <v>49000.0</v>
       </c>
-      <c r="L1" s="4">
+      <c r="M1" s="4">
         <v>50000.0</v>
       </c>
-      <c r="M1" s="4">
+      <c r="N1" s="4">
         <v>55000.0</v>
       </c>
-      <c r="N1" s="4">
+      <c r="O1" s="4">
         <v>58000.0</v>
       </c>
-      <c r="O1" s="4">
+      <c r="P1" s="4">
         <v>61000.0</v>
       </c>
-      <c r="P1" s="4">
+      <c r="Q1" s="4">
         <v>63000.0</v>
       </c>
-      <c r="Q1" s="4">
+      <c r="R1" s="4">
         <v>65000.0</v>
       </c>
-      <c r="R1" s="4">
+      <c r="S1" s="4">
         <v>67000.0</v>
       </c>
-      <c r="S1" s="4">
+      <c r="T1" s="4">
         <v>69000.0</v>
       </c>
-      <c r="T1" s="4">
+      <c r="U1" s="4">
         <v>77000.0</v>
       </c>
-      <c r="U1" s="4">
+      <c r="V1" s="4">
         <v>80000.0</v>
       </c>
-      <c r="V1" s="4">
+      <c r="W1" s="4">
         <v>90000.0</v>
       </c>
-      <c r="W1" s="4">
+      <c r="X1" s="4">
         <v>100000.0</v>
       </c>
-      <c r="X1" s="4">
+      <c r="Y1" s="4">
         <v>110000.0</v>
       </c>
-      <c r="Y1" s="4">
+      <c r="Z1" s="4">
         <v>130000.0</v>
       </c>
     </row>
@@ -1564,6 +1567,9 @@
       <c r="Y2" s="4">
         <v>0.0</v>
       </c>
+      <c r="Z2" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
@@ -1641,6 +1647,9 @@
       <c r="Y3" s="4">
         <v>0.0</v>
       </c>
+      <c r="Z3" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
@@ -1718,6 +1727,9 @@
       <c r="Y4" s="4">
         <v>0.0</v>
       </c>
+      <c r="Z4" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
@@ -1730,62 +1742,62 @@
         <v>133000.0</v>
       </c>
       <c r="D5" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E5" s="4">
+      <c r="F5" s="4">
         <v>210000.0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>228000.0</v>
       </c>
       <c r="G5" s="4">
         <v>228000.0</v>
       </c>
       <c r="H5" s="4">
+        <v>228000.0</v>
+      </c>
+      <c r="I5" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I5" s="4">
+      <c r="J5" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J5" s="4">
+      <c r="K5" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M5" s="4">
+      <c r="N5" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N5" s="4">
+      <c r="O5" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O5" s="4">
+      <c r="P5" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P5" s="4">
+      <c r="Q5" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="R5" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R5" s="4">
+      <c r="S5" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S5" s="4">
+      <c r="T5" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T5" s="4">
+      <c r="U5" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U5" s="4">
+      <c r="V5" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V5" s="4">
-        <v>500000.0</v>
-      </c>
       <c r="W5" s="4">
         <v>500000.0</v>
       </c>
@@ -1793,6 +1805,9 @@
         <v>500000.0</v>
       </c>
       <c r="Y5" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z5" s="4">
         <v>500000.0</v>
       </c>
     </row>
@@ -1807,62 +1822,62 @@
         <v>133000.0</v>
       </c>
       <c r="D6" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E6" s="4">
+      <c r="F6" s="4">
         <v>210000.0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>228000.0</v>
       </c>
       <c r="G6" s="4">
         <v>228000.0</v>
       </c>
       <c r="H6" s="4">
+        <v>228000.0</v>
+      </c>
+      <c r="I6" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I6" s="4">
+      <c r="J6" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J6" s="4">
+      <c r="K6" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K6" s="4">
+      <c r="L6" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L6" s="4">
+      <c r="M6" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M6" s="4">
+      <c r="N6" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N6" s="4">
+      <c r="O6" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O6" s="4">
+      <c r="P6" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P6" s="4">
+      <c r="Q6" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="R6" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R6" s="4">
+      <c r="S6" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S6" s="4">
+      <c r="T6" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T6" s="4">
+      <c r="U6" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U6" s="4">
+      <c r="V6" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V6" s="4">
-        <v>500000.0</v>
-      </c>
       <c r="W6" s="4">
         <v>500000.0</v>
       </c>
@@ -1870,6 +1885,9 @@
         <v>500000.0</v>
       </c>
       <c r="Y6" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z6" s="4">
         <v>500000.0</v>
       </c>
     </row>
@@ -1884,62 +1902,62 @@
         <v>133000.0</v>
       </c>
       <c r="D7" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <v>210000.0</v>
-      </c>
-      <c r="F7" s="4">
-        <v>228000.0</v>
       </c>
       <c r="G7" s="4">
         <v>228000.0</v>
       </c>
       <c r="H7" s="4">
+        <v>228000.0</v>
+      </c>
+      <c r="I7" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I7" s="4">
+      <c r="J7" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J7" s="4">
+      <c r="K7" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K7" s="4">
+      <c r="L7" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L7" s="4">
+      <c r="M7" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M7" s="4">
+      <c r="N7" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N7" s="4">
+      <c r="O7" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O7" s="4">
+      <c r="P7" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P7" s="4">
+      <c r="Q7" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="R7" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R7" s="4">
+      <c r="S7" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S7" s="4">
+      <c r="T7" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T7" s="4">
+      <c r="U7" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U7" s="4">
+      <c r="V7" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V7" s="4">
-        <v>500000.0</v>
-      </c>
       <c r="W7" s="4">
         <v>500000.0</v>
       </c>
@@ -1947,6 +1965,9 @@
         <v>500000.0</v>
       </c>
       <c r="Y7" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z7" s="4">
         <v>500000.0</v>
       </c>
     </row>
@@ -1961,62 +1982,62 @@
         <v>133000.0</v>
       </c>
       <c r="D8" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E8" s="4">
+      <c r="F8" s="4">
         <v>210000.0</v>
-      </c>
-      <c r="F8" s="4">
-        <v>228000.0</v>
       </c>
       <c r="G8" s="4">
         <v>228000.0</v>
       </c>
       <c r="H8" s="4">
+        <v>228000.0</v>
+      </c>
+      <c r="I8" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I8" s="4">
+      <c r="J8" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J8" s="4">
+      <c r="K8" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K8" s="4">
+      <c r="L8" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L8" s="4">
+      <c r="M8" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M8" s="4">
+      <c r="N8" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N8" s="4">
+      <c r="O8" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O8" s="4">
+      <c r="P8" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P8" s="4">
+      <c r="Q8" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="R8" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R8" s="4">
+      <c r="S8" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S8" s="4">
+      <c r="T8" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T8" s="4">
+      <c r="U8" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U8" s="4">
+      <c r="V8" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V8" s="4">
-        <v>500000.0</v>
-      </c>
       <c r="W8" s="4">
         <v>500000.0</v>
       </c>
@@ -2024,6 +2045,9 @@
         <v>500000.0</v>
       </c>
       <c r="Y8" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z8" s="4">
         <v>500000.0</v>
       </c>
     </row>
@@ -2038,62 +2062,62 @@
         <v>133000.0</v>
       </c>
       <c r="D9" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E9" s="4">
+      <c r="F9" s="4">
         <v>210000.0</v>
-      </c>
-      <c r="F9" s="4">
-        <v>228000.0</v>
       </c>
       <c r="G9" s="4">
         <v>228000.0</v>
       </c>
       <c r="H9" s="4">
+        <v>228000.0</v>
+      </c>
+      <c r="I9" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I9" s="4">
+      <c r="J9" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J9" s="4">
+      <c r="K9" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K9" s="4">
+      <c r="L9" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L9" s="4">
+      <c r="M9" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M9" s="4">
+      <c r="N9" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N9" s="4">
+      <c r="O9" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O9" s="4">
+      <c r="P9" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P9" s="4">
+      <c r="Q9" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="R9" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R9" s="4">
+      <c r="S9" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S9" s="4">
+      <c r="T9" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T9" s="4">
+      <c r="U9" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U9" s="4">
+      <c r="V9" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V9" s="4">
-        <v>500000.0</v>
-      </c>
       <c r="W9" s="4">
         <v>500000.0</v>
       </c>
@@ -2101,6 +2125,9 @@
         <v>500000.0</v>
       </c>
       <c r="Y9" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z9" s="4">
         <v>500000.0</v>
       </c>
     </row>
@@ -2115,62 +2142,62 @@
         <v>133000.0</v>
       </c>
       <c r="D10" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" s="4">
         <v>210000.0</v>
-      </c>
-      <c r="F10" s="4">
-        <v>228000.0</v>
       </c>
       <c r="G10" s="4">
         <v>228000.0</v>
       </c>
       <c r="H10" s="4">
+        <v>228000.0</v>
+      </c>
+      <c r="I10" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I10" s="4">
+      <c r="J10" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J10" s="4">
+      <c r="K10" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K10" s="4">
+      <c r="L10" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L10" s="4">
+      <c r="M10" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M10" s="4">
+      <c r="N10" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N10" s="4">
+      <c r="O10" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O10" s="4">
+      <c r="P10" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P10" s="4">
+      <c r="Q10" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="R10" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R10" s="4">
+      <c r="S10" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S10" s="4">
+      <c r="T10" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T10" s="4">
+      <c r="U10" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U10" s="4">
+      <c r="V10" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V10" s="4">
-        <v>500000.0</v>
-      </c>
       <c r="W10" s="4">
         <v>500000.0</v>
       </c>
@@ -2178,6 +2205,9 @@
         <v>500000.0</v>
       </c>
       <c r="Y10" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z10" s="4">
         <v>500000.0</v>
       </c>
     </row>
@@ -2192,69 +2222,72 @@
         <v>42000.0</v>
       </c>
       <c r="D11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="4">
         <v>60000.0</v>
       </c>
-      <c r="E11" s="4">
+      <c r="F11" s="4">
         <v>69000.0</v>
       </c>
-      <c r="F11" s="4">
+      <c r="G11" s="4">
         <v>75000.0</v>
       </c>
-      <c r="G11" s="4">
+      <c r="H11" s="4">
         <v>77000.0</v>
       </c>
-      <c r="H11" s="4">
+      <c r="I11" s="4">
         <v>78000.0</v>
       </c>
-      <c r="I11" s="4">
+      <c r="J11" s="4">
         <v>85000.0</v>
       </c>
-      <c r="J11" s="4">
+      <c r="K11" s="4">
         <v>86000.0</v>
       </c>
-      <c r="K11" s="4">
+      <c r="L11" s="4">
         <v>89000.0</v>
       </c>
-      <c r="L11" s="4">
+      <c r="M11" s="4">
         <v>91000.0</v>
       </c>
-      <c r="M11" s="4">
+      <c r="N11" s="4">
         <v>100000.0</v>
       </c>
-      <c r="N11" s="4">
+      <c r="O11" s="4">
         <v>107000.0</v>
       </c>
-      <c r="O11" s="4">
+      <c r="P11" s="4">
         <v>111000.0</v>
       </c>
-      <c r="P11" s="4">
+      <c r="Q11" s="4">
         <v>116000.0</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="R11" s="4">
         <v>119000.0</v>
       </c>
-      <c r="R11" s="4">
+      <c r="S11" s="4">
         <v>122000.0</v>
       </c>
-      <c r="S11" s="4">
+      <c r="T11" s="4">
         <v>127000.0</v>
       </c>
-      <c r="T11" s="4">
+      <c r="U11" s="4">
         <v>139000.0</v>
       </c>
-      <c r="U11" s="4">
+      <c r="V11" s="4">
         <v>147000.0</v>
       </c>
-      <c r="V11" s="4">
+      <c r="W11" s="4">
         <v>150000.0</v>
       </c>
-      <c r="W11" s="4">
+      <c r="X11" s="4">
         <v>183000.0</v>
       </c>
-      <c r="X11" s="4">
+      <c r="Y11" s="4">
         <v>201000.0</v>
       </c>
-      <c r="Y11" s="4">
+      <c r="Z11" s="4">
         <v>250000.0</v>
       </c>
     </row>
@@ -2269,69 +2302,72 @@
         <v>42000.0</v>
       </c>
       <c r="D12" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E12" s="4">
         <v>60000.0</v>
       </c>
-      <c r="E12" s="4">
+      <c r="F12" s="4">
         <v>69000.0</v>
       </c>
-      <c r="F12" s="4">
+      <c r="G12" s="4">
         <v>75000.0</v>
       </c>
-      <c r="G12" s="4">
+      <c r="H12" s="4">
         <v>77000.0</v>
       </c>
-      <c r="H12" s="4">
+      <c r="I12" s="4">
         <v>78000.0</v>
       </c>
-      <c r="I12" s="4">
+      <c r="J12" s="4">
         <v>85000.0</v>
       </c>
-      <c r="J12" s="4">
+      <c r="K12" s="4">
         <v>86000.0</v>
       </c>
-      <c r="K12" s="4">
+      <c r="L12" s="4">
         <v>89000.0</v>
       </c>
-      <c r="L12" s="4">
+      <c r="M12" s="4">
         <v>91000.0</v>
       </c>
-      <c r="M12" s="4">
+      <c r="N12" s="4">
         <v>100000.0</v>
       </c>
-      <c r="N12" s="4">
+      <c r="O12" s="4">
         <v>107000.0</v>
       </c>
-      <c r="O12" s="4">
+      <c r="P12" s="4">
         <v>111000.0</v>
       </c>
-      <c r="P12" s="4">
+      <c r="Q12" s="4">
         <v>116000.0</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="R12" s="4">
         <v>119000.0</v>
       </c>
-      <c r="R12" s="4">
+      <c r="S12" s="4">
         <v>122000.0</v>
       </c>
-      <c r="S12" s="4">
+      <c r="T12" s="4">
         <v>127000.0</v>
       </c>
-      <c r="T12" s="4">
+      <c r="U12" s="4">
         <v>139000.0</v>
       </c>
-      <c r="U12" s="4">
+      <c r="V12" s="4">
         <v>147000.0</v>
       </c>
-      <c r="V12" s="4">
+      <c r="W12" s="4">
         <v>150000.0</v>
       </c>
-      <c r="W12" s="4">
+      <c r="X12" s="4">
         <v>183000.0</v>
       </c>
-      <c r="X12" s="4">
+      <c r="Y12" s="4">
         <v>201000.0</v>
       </c>
-      <c r="Y12" s="4">
+      <c r="Z12" s="4">
         <v>250000.0</v>
       </c>
     </row>
@@ -2346,69 +2382,72 @@
         <v>42000.0</v>
       </c>
       <c r="D13" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="4">
         <v>60000.0</v>
       </c>
-      <c r="E13" s="4">
+      <c r="F13" s="4">
         <v>69000.0</v>
       </c>
-      <c r="F13" s="4">
+      <c r="G13" s="4">
         <v>75000.0</v>
       </c>
-      <c r="G13" s="4">
+      <c r="H13" s="4">
         <v>77000.0</v>
       </c>
-      <c r="H13" s="4">
+      <c r="I13" s="4">
         <v>78000.0</v>
       </c>
-      <c r="I13" s="4">
+      <c r="J13" s="4">
         <v>85000.0</v>
       </c>
-      <c r="J13" s="4">
+      <c r="K13" s="4">
         <v>86000.0</v>
       </c>
-      <c r="K13" s="4">
+      <c r="L13" s="4">
         <v>89000.0</v>
       </c>
-      <c r="L13" s="4">
+      <c r="M13" s="4">
         <v>91000.0</v>
       </c>
-      <c r="M13" s="4">
+      <c r="N13" s="4">
         <v>100000.0</v>
       </c>
-      <c r="N13" s="4">
+      <c r="O13" s="4">
         <v>107000.0</v>
       </c>
-      <c r="O13" s="4">
+      <c r="P13" s="4">
         <v>111000.0</v>
       </c>
-      <c r="P13" s="4">
+      <c r="Q13" s="4">
         <v>116000.0</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="R13" s="4">
         <v>119000.0</v>
       </c>
-      <c r="R13" s="4">
+      <c r="S13" s="4">
         <v>122000.0</v>
       </c>
-      <c r="S13" s="4">
+      <c r="T13" s="4">
         <v>127000.0</v>
       </c>
-      <c r="T13" s="4">
+      <c r="U13" s="4">
         <v>139000.0</v>
       </c>
-      <c r="U13" s="4">
+      <c r="V13" s="4">
         <v>147000.0</v>
       </c>
-      <c r="V13" s="4">
+      <c r="W13" s="4">
         <v>150000.0</v>
       </c>
-      <c r="W13" s="4">
+      <c r="X13" s="4">
         <v>183000.0</v>
       </c>
-      <c r="X13" s="4">
+      <c r="Y13" s="4">
         <v>201000.0</v>
       </c>
-      <c r="Y13" s="4">
+      <c r="Z13" s="4">
         <v>250000.0</v>
       </c>
     </row>
@@ -2423,61 +2462,61 @@
         <v>181000.0</v>
       </c>
       <c r="D14" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E14" s="4">
         <v>246000.0</v>
       </c>
-      <c r="E14" s="4">
+      <c r="F14" s="4">
         <v>281000.0</v>
       </c>
-      <c r="F14" s="4">
+      <c r="G14" s="4">
         <v>305000.0</v>
       </c>
-      <c r="G14" s="4">
+      <c r="H14" s="4">
         <v>311000.0</v>
       </c>
-      <c r="H14" s="4">
+      <c r="I14" s="4">
         <v>317000.0</v>
       </c>
-      <c r="I14" s="4">
+      <c r="J14" s="4">
         <v>341000.0</v>
       </c>
-      <c r="J14" s="4">
+      <c r="K14" s="4">
         <v>347000.0</v>
       </c>
-      <c r="K14" s="4">
+      <c r="L14" s="4">
         <v>358000.0</v>
       </c>
-      <c r="L14" s="4">
+      <c r="M14" s="4">
         <v>364000.0</v>
       </c>
-      <c r="M14" s="4">
+      <c r="N14" s="4">
         <v>400000.0</v>
       </c>
-      <c r="N14" s="4">
+      <c r="O14" s="4">
         <v>423000.0</v>
       </c>
-      <c r="O14" s="4">
+      <c r="P14" s="4">
         <v>441000.0</v>
       </c>
-      <c r="P14" s="4">
+      <c r="Q14" s="4">
         <v>459000.0</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="R14" s="4">
         <v>471000.0</v>
       </c>
-      <c r="R14" s="4">
+      <c r="S14" s="4">
         <v>482000.0</v>
       </c>
-      <c r="S14" s="4">
-        <v>500000.0</v>
-      </c>
       <c r="T14" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="U14" s="4">
         <v>547000.0</v>
       </c>
-      <c r="U14" s="4">
+      <c r="V14" s="4">
         <v>600000.0</v>
-      </c>
-      <c r="V14" s="4">
-        <v>700000.0</v>
       </c>
       <c r="W14" s="4">
         <v>700000.0</v>
@@ -2486,6 +2525,9 @@
         <v>700000.0</v>
       </c>
       <c r="Y14" s="4">
+        <v>700000.0</v>
+      </c>
+      <c r="Z14" s="4">
         <v>700000.0</v>
       </c>
     </row>
@@ -2500,53 +2542,53 @@
         <v>133000.0</v>
       </c>
       <c r="D15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E15" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E15" s="4">
+      <c r="F15" s="4">
         <v>210000.0</v>
       </c>
-      <c r="F15" s="4">
+      <c r="G15" s="4">
         <v>228000.0</v>
       </c>
-      <c r="G15" s="4">
+      <c r="H15" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H15" s="4">
+      <c r="I15" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I15" s="4">
+      <c r="J15" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J15" s="4">
+      <c r="K15" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K15" s="4">
+      <c r="L15" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L15" s="4">
+      <c r="M15" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M15" s="4">
+      <c r="N15" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N15" s="4">
+      <c r="O15" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O15" s="4">
+      <c r="P15" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P15" s="4">
+      <c r="Q15" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="R15" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R15" s="4">
+      <c r="S15" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S15" s="4">
-        <v>500000.0</v>
-      </c>
       <c r="T15" s="4">
         <v>500000.0</v>
       </c>
@@ -2563,6 +2605,9 @@
         <v>500000.0</v>
       </c>
       <c r="Y15" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z15" s="4">
         <v>500000.0</v>
       </c>
     </row>
@@ -2577,62 +2622,62 @@
         <v>133000.0</v>
       </c>
       <c r="D16" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E16" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E16" s="4">
+      <c r="F16" s="4">
         <v>210000.0</v>
       </c>
-      <c r="F16" s="4">
+      <c r="G16" s="4">
         <v>228000.0</v>
       </c>
-      <c r="G16" s="4">
+      <c r="H16" s="4">
         <v>233000.0</v>
       </c>
-      <c r="H16" s="4">
+      <c r="I16" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I16" s="4">
+      <c r="J16" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J16" s="4">
+      <c r="K16" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K16" s="4">
+      <c r="L16" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L16" s="4">
+      <c r="M16" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M16" s="4">
+      <c r="N16" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N16" s="4">
+      <c r="O16" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O16" s="4">
+      <c r="P16" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P16" s="4">
+      <c r="Q16" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="R16" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R16" s="4">
+      <c r="S16" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S16" s="4">
+      <c r="T16" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T16" s="4">
+      <c r="U16" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U16" s="4">
+      <c r="V16" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V16" s="4">
-        <v>500000.0</v>
-      </c>
       <c r="W16" s="4">
         <v>500000.0</v>
       </c>
@@ -2640,6 +2685,9 @@
         <v>500000.0</v>
       </c>
       <c r="Y16" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z16" s="4">
         <v>500000.0</v>
       </c>
     </row>
@@ -2654,62 +2702,62 @@
         <v>133000.0</v>
       </c>
       <c r="D17" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E17" s="4">
         <v>183000.0</v>
       </c>
-      <c r="E17" s="4">
+      <c r="F17" s="4">
         <v>210000.0</v>
-      </c>
-      <c r="F17" s="4">
-        <v>228000.0</v>
       </c>
       <c r="G17" s="4">
         <v>228000.0</v>
       </c>
       <c r="H17" s="4">
+        <v>228000.0</v>
+      </c>
+      <c r="I17" s="4">
         <v>237000.0</v>
       </c>
-      <c r="I17" s="4">
+      <c r="J17" s="4">
         <v>255000.0</v>
       </c>
-      <c r="J17" s="4">
+      <c r="K17" s="4">
         <v>260000.0</v>
       </c>
-      <c r="K17" s="4">
+      <c r="L17" s="4">
         <v>269000.0</v>
       </c>
-      <c r="L17" s="4">
+      <c r="M17" s="4">
         <v>273000.0</v>
       </c>
-      <c r="M17" s="4">
+      <c r="N17" s="4">
         <v>300000.0</v>
       </c>
-      <c r="N17" s="4">
+      <c r="O17" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O17" s="4">
+      <c r="P17" s="4">
         <v>332000.0</v>
       </c>
-      <c r="P17" s="4">
+      <c r="Q17" s="4">
         <v>346000.0</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="R17" s="4">
         <v>355000.0</v>
       </c>
-      <c r="R17" s="4">
+      <c r="S17" s="4">
         <v>364000.0</v>
       </c>
-      <c r="S17" s="4">
+      <c r="T17" s="4">
         <v>377000.0</v>
       </c>
-      <c r="T17" s="4">
+      <c r="U17" s="4">
         <v>413000.0</v>
       </c>
-      <c r="U17" s="4">
+      <c r="V17" s="4">
         <v>450000.0</v>
       </c>
-      <c r="V17" s="4">
-        <v>500000.0</v>
-      </c>
       <c r="W17" s="4">
         <v>500000.0</v>
       </c>
@@ -2717,6 +2765,9 @@
         <v>500000.0</v>
       </c>
       <c r="Y17" s="4">
+        <v>500000.0</v>
+      </c>
+      <c r="Z17" s="4">
         <v>500000.0</v>
       </c>
     </row>
@@ -2731,61 +2782,61 @@
         <v>82000.0</v>
       </c>
       <c r="D18" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E18" s="4">
         <v>156000.0</v>
       </c>
-      <c r="E18" s="4">
+      <c r="F18" s="4">
         <v>196000.0</v>
       </c>
-      <c r="F18" s="4">
+      <c r="G18" s="4">
         <v>223000.0</v>
       </c>
-      <c r="G18" s="4">
+      <c r="H18" s="4">
         <v>230000.0</v>
       </c>
-      <c r="H18" s="4">
+      <c r="I18" s="4">
         <v>236000.0</v>
       </c>
-      <c r="I18" s="4">
+      <c r="J18" s="4">
         <v>263000.0</v>
       </c>
-      <c r="J18" s="4">
+      <c r="K18" s="4">
         <v>270000.0</v>
       </c>
-      <c r="K18" s="4">
+      <c r="L18" s="4">
         <v>283000.0</v>
       </c>
-      <c r="L18" s="4">
+      <c r="M18" s="4">
         <v>290000.0</v>
       </c>
-      <c r="M18" s="4">
+      <c r="N18" s="4">
         <v>330000.0</v>
       </c>
-      <c r="N18" s="4">
+      <c r="O18" s="4">
         <v>357000.0</v>
       </c>
-      <c r="O18" s="4">
+      <c r="P18" s="4">
         <v>377000.0</v>
       </c>
-      <c r="P18" s="4">
+      <c r="Q18" s="4">
         <v>398000.0</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="R18" s="4">
         <v>411000.0</v>
       </c>
-      <c r="R18" s="4">
+      <c r="S18" s="4">
         <v>425000.0</v>
       </c>
-      <c r="S18" s="4">
+      <c r="T18" s="4">
         <v>445000.0</v>
       </c>
-      <c r="T18" s="4">
+      <c r="U18" s="4">
         <v>498000.0</v>
       </c>
-      <c r="U18" s="4">
+      <c r="V18" s="4">
         <v>530000.0</v>
-      </c>
-      <c r="V18" s="4">
-        <v>600000.0</v>
       </c>
       <c r="W18" s="4">
         <v>600000.0</v>
@@ -2794,6 +2845,9 @@
         <v>600000.0</v>
       </c>
       <c r="Y18" s="4">
+        <v>600000.0</v>
+      </c>
+      <c r="Z18" s="4">
         <v>600000.0</v>
       </c>
     </row>
@@ -2873,6 +2927,9 @@
       <c r="Y19" s="4">
         <v>0.0</v>
       </c>
+      <c r="Z19" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
@@ -2885,69 +2942,72 @@
         <v>42000.0</v>
       </c>
       <c r="D20" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E20" s="4">
         <v>60000.0</v>
       </c>
-      <c r="E20" s="4">
+      <c r="F20" s="4">
         <v>69000.0</v>
       </c>
-      <c r="F20" s="4">
+      <c r="G20" s="4">
         <v>75000.0</v>
       </c>
-      <c r="G20" s="4">
+      <c r="H20" s="4">
         <v>77000.0</v>
       </c>
-      <c r="H20" s="4">
+      <c r="I20" s="4">
         <v>78000.0</v>
       </c>
-      <c r="I20" s="4">
+      <c r="J20" s="4">
         <v>85000.0</v>
       </c>
-      <c r="J20" s="4">
+      <c r="K20" s="4">
         <v>86000.0</v>
       </c>
-      <c r="K20" s="4">
+      <c r="L20" s="4">
         <v>89000.0</v>
       </c>
-      <c r="L20" s="4">
+      <c r="M20" s="4">
         <v>91000.0</v>
       </c>
-      <c r="M20" s="4">
+      <c r="N20" s="4">
         <v>100000.0</v>
       </c>
-      <c r="N20" s="4">
+      <c r="O20" s="4">
         <v>107000.0</v>
       </c>
-      <c r="O20" s="4">
+      <c r="P20" s="4">
         <v>111000.0</v>
       </c>
-      <c r="P20" s="4">
+      <c r="Q20" s="4">
         <v>116000.0</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="R20" s="4">
         <v>119000.0</v>
       </c>
-      <c r="R20" s="4">
+      <c r="S20" s="4">
         <v>122000.0</v>
       </c>
-      <c r="S20" s="4">
+      <c r="T20" s="4">
         <v>127000.0</v>
       </c>
-      <c r="T20" s="4">
+      <c r="U20" s="4">
         <v>137000.0</v>
       </c>
-      <c r="U20" s="4">
+      <c r="V20" s="4">
         <v>147000.0</v>
       </c>
-      <c r="V20" s="4">
+      <c r="W20" s="4">
         <v>150000.0</v>
       </c>
-      <c r="W20" s="4">
+      <c r="X20" s="4">
         <v>183000.0</v>
       </c>
-      <c r="X20" s="4">
+      <c r="Y20" s="4">
         <v>201000.0</v>
       </c>
-      <c r="Y20" s="4">
+      <c r="Z20" s="4">
         <v>250000.0</v>
       </c>
     </row>
@@ -2962,69 +3022,72 @@
         <v>42000.0</v>
       </c>
       <c r="D21" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E21" s="4">
         <v>60000.0</v>
       </c>
-      <c r="E21" s="4">
+      <c r="F21" s="4">
         <v>69000.0</v>
       </c>
-      <c r="F21" s="4">
+      <c r="G21" s="4">
         <v>75000.0</v>
       </c>
-      <c r="G21" s="4">
+      <c r="H21" s="4">
         <v>77000.0</v>
       </c>
-      <c r="H21" s="4">
+      <c r="I21" s="4">
         <v>78000.0</v>
       </c>
-      <c r="I21" s="4">
+      <c r="J21" s="4">
         <v>85000.0</v>
       </c>
-      <c r="J21" s="4">
+      <c r="K21" s="4">
         <v>86000.0</v>
       </c>
-      <c r="K21" s="4">
+      <c r="L21" s="4">
         <v>89000.0</v>
       </c>
-      <c r="L21" s="4">
+      <c r="M21" s="4">
         <v>91000.0</v>
       </c>
-      <c r="M21" s="4">
+      <c r="N21" s="4">
         <v>100000.0</v>
       </c>
-      <c r="N21" s="4">
+      <c r="O21" s="4">
         <v>107000.0</v>
       </c>
-      <c r="O21" s="4">
+      <c r="P21" s="4">
         <v>111000.0</v>
       </c>
-      <c r="P21" s="4">
+      <c r="Q21" s="4">
         <v>116000.0</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="R21" s="4">
         <v>119000.0</v>
       </c>
-      <c r="R21" s="4">
+      <c r="S21" s="4">
         <v>122000.0</v>
       </c>
-      <c r="S21" s="4">
+      <c r="T21" s="4">
         <v>127000.0</v>
       </c>
-      <c r="T21" s="4">
+      <c r="U21" s="4">
         <v>139000.0</v>
       </c>
-      <c r="U21" s="4">
+      <c r="V21" s="4">
         <v>147000.0</v>
       </c>
-      <c r="V21" s="4">
+      <c r="W21" s="4">
         <v>150000.0</v>
       </c>
-      <c r="W21" s="4">
+      <c r="X21" s="4">
         <v>183000.0</v>
       </c>
-      <c r="X21" s="4">
+      <c r="Y21" s="4">
         <v>201000.0</v>
       </c>
-      <c r="Y21" s="4">
+      <c r="Z21" s="4">
         <v>250000.0</v>
       </c>
     </row>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -1408,7 +1408,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.25"/>
-    <col customWidth="1" min="2" max="26" width="7.13"/>
+    <col customWidth="1" min="2" max="27" width="7.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1488,6 +1488,9 @@
         <v>110000.0</v>
       </c>
       <c r="Z1" s="4">
+        <v>120000.0</v>
+      </c>
+      <c r="AA1" s="4">
         <v>130000.0</v>
       </c>
     </row>
@@ -1570,6 +1573,9 @@
       <c r="Z2" s="4">
         <v>0.0</v>
       </c>
+      <c r="AA2" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
@@ -1650,6 +1656,9 @@
       <c r="Z3" s="4">
         <v>0.0</v>
       </c>
+      <c r="AA3" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
@@ -1730,6 +1739,9 @@
       <c r="Z4" s="4">
         <v>0.0</v>
       </c>
+      <c r="AA4" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
@@ -1810,6 +1822,9 @@
       <c r="Z5" s="4">
         <v>500000.0</v>
       </c>
+      <c r="AA5" s="4">
+        <v>500000.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
@@ -1890,6 +1905,9 @@
       <c r="Z6" s="4">
         <v>500000.0</v>
       </c>
+      <c r="AA6" s="4">
+        <v>500000.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
@@ -1970,6 +1988,9 @@
       <c r="Z7" s="4">
         <v>500000.0</v>
       </c>
+      <c r="AA7" s="4">
+        <v>500000.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
@@ -2050,6 +2071,9 @@
       <c r="Z8" s="4">
         <v>500000.0</v>
       </c>
+      <c r="AA8" s="4">
+        <v>500000.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
@@ -2130,6 +2154,9 @@
       <c r="Z9" s="4">
         <v>500000.0</v>
       </c>
+      <c r="AA9" s="4">
+        <v>500000.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
@@ -2210,6 +2237,9 @@
       <c r="Z10" s="4">
         <v>500000.0</v>
       </c>
+      <c r="AA10" s="4">
+        <v>500000.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
@@ -2288,6 +2318,9 @@
         <v>201000.0</v>
       </c>
       <c r="Z11" s="4">
+        <v>221000.0</v>
+      </c>
+      <c r="AA11" s="4">
         <v>250000.0</v>
       </c>
     </row>
@@ -2368,6 +2401,9 @@
         <v>201000.0</v>
       </c>
       <c r="Z12" s="4">
+        <v>221000.0</v>
+      </c>
+      <c r="AA12" s="4">
         <v>250000.0</v>
       </c>
     </row>
@@ -2448,6 +2484,9 @@
         <v>201000.0</v>
       </c>
       <c r="Z13" s="4">
+        <v>221000.0</v>
+      </c>
+      <c r="AA13" s="4">
         <v>250000.0</v>
       </c>
     </row>
@@ -2530,6 +2569,9 @@
       <c r="Z14" s="4">
         <v>700000.0</v>
       </c>
+      <c r="AA14" s="4">
+        <v>700000.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
@@ -2610,6 +2652,9 @@
       <c r="Z15" s="4">
         <v>500000.0</v>
       </c>
+      <c r="AA15" s="4">
+        <v>500000.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
@@ -2690,6 +2735,9 @@
       <c r="Z16" s="4">
         <v>500000.0</v>
       </c>
+      <c r="AA16" s="4">
+        <v>500000.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
@@ -2770,6 +2818,9 @@
       <c r="Z17" s="4">
         <v>500000.0</v>
       </c>
+      <c r="AA17" s="4">
+        <v>500000.0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
@@ -2850,6 +2901,9 @@
       <c r="Z18" s="4">
         <v>600000.0</v>
       </c>
+      <c r="AA18" s="4">
+        <v>600000.0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
@@ -2930,6 +2984,9 @@
       <c r="Z19" s="4">
         <v>0.0</v>
       </c>
+      <c r="AA19" s="4">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
@@ -3008,6 +3065,9 @@
         <v>201000.0</v>
       </c>
       <c r="Z20" s="4">
+        <v>221000.0</v>
+      </c>
+      <c r="AA20" s="4">
         <v>250000.0</v>
       </c>
     </row>
@@ -3088,6 +3148,9 @@
         <v>201000.0</v>
       </c>
       <c r="Z21" s="4">
+        <v>221000.0</v>
+      </c>
+      <c r="AA21" s="4">
         <v>250000.0</v>
       </c>
     </row>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -118,7 +118,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -129,12 +129,17 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
-      <name val="&quot;맑은 고딕&quot;"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -158,11 +163,11 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -390,15 +395,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="26.88"/>
-    <col customWidth="1" min="2" max="2" width="11.13"/>
-    <col customWidth="1" min="3" max="3" width="12.63"/>
-    <col customWidth="1" min="4" max="4" width="11.13"/>
-    <col customWidth="1" min="5" max="5" width="12.63"/>
-    <col customWidth="1" min="6" max="7" width="14.13"/>
-    <col customWidth="1" min="8" max="9" width="15.75"/>
-    <col customWidth="1" min="10" max="11" width="14.13"/>
-    <col customWidth="1" min="12" max="13" width="15.75"/>
+    <col customWidth="1" min="1" max="1" width="19.25"/>
+    <col customWidth="1" min="2" max="2" width="12.13"/>
+    <col customWidth="1" min="3" max="3" width="13.75"/>
+    <col customWidth="1" min="4" max="4" width="12.13"/>
+    <col customWidth="1" min="5" max="5" width="13.75"/>
+    <col customWidth="1" min="6" max="7" width="15.5"/>
+    <col customWidth="1" min="8" max="9" width="17.13"/>
+    <col customWidth="1" min="10" max="11" width="15.5"/>
+    <col customWidth="1" min="12" max="13" width="17.13"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -1759,7 +1759,7 @@
         <v>133000.0</v>
       </c>
       <c r="D5" s="4">
-        <v>0.0</v>
+        <v>151000.0</v>
       </c>
       <c r="E5" s="4">
         <v>183000.0</v>
@@ -1842,7 +1842,7 @@
         <v>133000.0</v>
       </c>
       <c r="D6" s="4">
-        <v>0.0</v>
+        <v>151000.0</v>
       </c>
       <c r="E6" s="4">
         <v>183000.0</v>
@@ -1925,7 +1925,7 @@
         <v>133000.0</v>
       </c>
       <c r="D7" s="4">
-        <v>0.0</v>
+        <v>151000.0</v>
       </c>
       <c r="E7" s="4">
         <v>183000.0</v>
@@ -2008,7 +2008,7 @@
         <v>133000.0</v>
       </c>
       <c r="D8" s="4">
-        <v>0.0</v>
+        <v>151000.0</v>
       </c>
       <c r="E8" s="4">
         <v>183000.0</v>
@@ -2091,7 +2091,7 @@
         <v>133000.0</v>
       </c>
       <c r="D9" s="4">
-        <v>0.0</v>
+        <v>151000.0</v>
       </c>
       <c r="E9" s="4">
         <v>183000.0</v>
@@ -2174,7 +2174,7 @@
         <v>133000.0</v>
       </c>
       <c r="D10" s="4">
-        <v>0.0</v>
+        <v>151000.0</v>
       </c>
       <c r="E10" s="4">
         <v>183000.0</v>
@@ -2257,7 +2257,7 @@
         <v>42000.0</v>
       </c>
       <c r="D11" s="4">
-        <v>0.0</v>
+        <v>49000.0</v>
       </c>
       <c r="E11" s="4">
         <v>60000.0</v>
@@ -2340,7 +2340,7 @@
         <v>42000.0</v>
       </c>
       <c r="D12" s="4">
-        <v>0.0</v>
+        <v>49000.0</v>
       </c>
       <c r="E12" s="4">
         <v>60000.0</v>
@@ -2423,7 +2423,7 @@
         <v>42000.0</v>
       </c>
       <c r="D13" s="4">
-        <v>0.0</v>
+        <v>49000.0</v>
       </c>
       <c r="E13" s="4">
         <v>60000.0</v>
@@ -2506,7 +2506,7 @@
         <v>181000.0</v>
       </c>
       <c r="D14" s="4">
-        <v>0.0</v>
+        <v>205000.0</v>
       </c>
       <c r="E14" s="4">
         <v>246000.0</v>
@@ -2589,7 +2589,7 @@
         <v>133000.0</v>
       </c>
       <c r="D15" s="4">
-        <v>0.0</v>
+        <v>151000.0</v>
       </c>
       <c r="E15" s="4">
         <v>183000.0</v>
@@ -2672,7 +2672,7 @@
         <v>133000.0</v>
       </c>
       <c r="D16" s="4">
-        <v>0.0</v>
+        <v>151000.0</v>
       </c>
       <c r="E16" s="4">
         <v>183000.0</v>
@@ -2755,7 +2755,7 @@
         <v>133000.0</v>
       </c>
       <c r="D17" s="4">
-        <v>0.0</v>
+        <v>151000.0</v>
       </c>
       <c r="E17" s="4">
         <v>183000.0</v>
@@ -2838,7 +2838,7 @@
         <v>82000.0</v>
       </c>
       <c r="D18" s="4">
-        <v>0.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E18" s="4">
         <v>156000.0</v>
@@ -3004,7 +3004,7 @@
         <v>42000.0</v>
       </c>
       <c r="D20" s="4">
-        <v>0.0</v>
+        <v>49000.0</v>
       </c>
       <c r="E20" s="4">
         <v>60000.0</v>
@@ -3087,7 +3087,7 @@
         <v>42000.0</v>
       </c>
       <c r="D21" s="4">
-        <v>0.0</v>
+        <v>49000.0</v>
       </c>
       <c r="E21" s="4">
         <v>60000.0</v>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -54,71 +54,71 @@
     <t>U_번이_갤캠스_저가</t>
   </si>
   <si>
-    <t>폴드8 울트라｜512기가</t>
+    <t>Z Fold8 Ultra 512G</t>
   </si>
   <si>
-    <t>폴드8｜512기가</t>
+    <t>Z Fold8 512G</t>
   </si>
   <si>
-    <t>플립8｜512기가</t>
+    <t>Z Flip8 512G</t>
   </si>
   <si>
-    <t>S26 울트라｜512기가</t>
+    <t>S26 Ultra 512G</t>
   </si>
   <si>
-    <t>S26 플러스｜512기가</t>
+    <t>S26+ 512G</t>
   </si>
   <si>
-    <t>S26｜512기가</t>
+    <t>S26 512G</t>
   </si>
   <si>
-    <t>S26 울트라｜256기가</t>
+    <t>S26 Ultra 256G</t>
   </si>
   <si>
-    <t>S26 플러스｜256기가</t>
+    <t>S26+ 256G</t>
   </si>
   <si>
-    <t>S26｜256기가</t>
+    <t>S26 256G</t>
   </si>
   <si>
-    <t>S25 울트라｜256기가</t>
+    <t>S25 Ultra 256G</t>
   </si>
   <si>
-    <t>S25 플러스｜256기가</t>
+    <t>S25+ 256G</t>
   </si>
   <si>
-    <t>S25｜256기가</t>
+    <t>S25 256G</t>
   </si>
   <si>
-    <t>S25 엣지｜256기가</t>
+    <t>S25 Edge 256G</t>
   </si>
   <si>
-    <t>S25 FE｜256기가</t>
+    <t>S25 FE</t>
   </si>
   <si>
-    <t>폴드7｜256기가</t>
+    <t>Z Fold7 256G</t>
   </si>
   <si>
-    <t>플립7｜256기가</t>
+    <t>Z Flip7 256G</t>
   </si>
   <si>
-    <t>플립7 FE｜256기가</t>
+    <t>Z Flip7 FE</t>
   </si>
   <si>
-    <t>A37 5G｜128기가</t>
+    <t>A37 5G</t>
   </si>
   <si>
-    <t>A36 5G｜128기가</t>
+    <t>A36 5G</t>
   </si>
   <si>
-    <t>A17 LTE｜128기가</t>
+    <t>A17 LTE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -129,12 +129,6 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -160,15 +154,15 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -393,7 +387,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.25"/>
     <col customWidth="1" min="2" max="2" width="12.13"/>
@@ -406,7 +400,7 @@
     <col customWidth="1" min="12" max="13" width="17.13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -446,10 +440,10 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2"/>
+      <c r="N1" s="1"/>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="1">
@@ -488,10 +482,10 @@
       <c r="M2" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N2" s="2"/>
+      <c r="N2" s="1"/>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="1">
@@ -530,10 +524,10 @@
       <c r="M3" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N3" s="2"/>
+      <c r="N3" s="1"/>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="1">
@@ -572,10 +566,10 @@
       <c r="M4" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N4" s="2"/>
+      <c r="N4" s="1"/>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="1">
@@ -614,10 +608,10 @@
       <c r="M5" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="N5" s="1"/>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="1">
@@ -656,10 +650,10 @@
       <c r="M6" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N6" s="2"/>
+      <c r="N6" s="1"/>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="1">
@@ -698,10 +692,10 @@
       <c r="M7" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N7" s="2"/>
+      <c r="N7" s="1"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="1">
@@ -740,10 +734,10 @@
       <c r="M8" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N8" s="2"/>
+      <c r="N8" s="1"/>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="1">
@@ -782,10 +776,10 @@
       <c r="M9" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N9" s="2"/>
+      <c r="N9" s="1"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="1">
@@ -824,10 +818,10 @@
       <c r="M10" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" s="1"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="1">
@@ -866,10 +860,10 @@
       <c r="M11" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N11" s="2"/>
+      <c r="N11" s="1"/>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="1">
@@ -908,10 +902,10 @@
       <c r="M12" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N12" s="2"/>
+      <c r="N12" s="1"/>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="1">
@@ -950,10 +944,10 @@
       <c r="M13" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N13" s="2"/>
+      <c r="N13" s="1"/>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="1">
@@ -992,10 +986,10 @@
       <c r="M14" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N14" s="2"/>
+      <c r="N14" s="1"/>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="1">
@@ -1034,10 +1028,10 @@
       <c r="M15" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N15" s="2"/>
+      <c r="N15" s="1"/>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="s">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="1">
@@ -1076,10 +1070,10 @@
       <c r="M16" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N16" s="2"/>
+      <c r="N16" s="1"/>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B17" s="1">
@@ -1118,10 +1112,10 @@
       <c r="M17" s="1">
         <v>50000.0</v>
       </c>
-      <c r="N17" s="2"/>
+      <c r="N17" s="1"/>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="s">
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="1">
@@ -1160,10 +1154,10 @@
       <c r="M18" s="1">
         <v>0.0</v>
       </c>
-      <c r="N18" s="2"/>
+      <c r="N18" s="1"/>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B19" s="1">
@@ -1202,10 +1196,10 @@
       <c r="M19" s="1">
         <v>100000.0</v>
       </c>
-      <c r="N19" s="2"/>
+      <c r="N19" s="1"/>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B20" s="1">
@@ -1244,10 +1238,10 @@
       <c r="M20" s="1">
         <v>100000.0</v>
       </c>
-      <c r="N20" s="2"/>
+      <c r="N20" s="1"/>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="1">
@@ -1286,120 +1280,1092 @@
       <c r="M21" s="1">
         <v>30000.0</v>
       </c>
-      <c r="N21" s="2"/>
+      <c r="N21" s="1"/>
     </row>
-    <row r="22">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
     </row>
-    <row r="23">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
     </row>
-    <row r="24">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
     </row>
-    <row r="25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
     </row>
-    <row r="26">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
     </row>
-    <row r="27">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
     </row>
-    <row r="28">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
     </row>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1410,13 +2376,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.25"/>
     <col customWidth="1" min="2" max="27" width="7.13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1499,8 +2465,8 @@
         <v>130000.0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="4">
@@ -1582,8 +2548,8 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="4">
@@ -1665,8 +2631,8 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="4">
@@ -1748,8 +2714,8 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="4">
@@ -1831,8 +2797,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="4">
@@ -1914,8 +2880,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="4">
@@ -1997,8 +2963,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="4">
@@ -2080,8 +3046,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="4">
@@ -2163,8 +3129,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="4">
@@ -2246,8 +3212,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="4">
@@ -2329,8 +3295,8 @@
         <v>250000.0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="4">
@@ -2412,8 +3378,8 @@
         <v>250000.0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="4">
@@ -2495,8 +3461,8 @@
         <v>250000.0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="4">
@@ -2578,8 +3544,8 @@
         <v>700000.0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="4">
@@ -2661,8 +3627,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="4">
@@ -2744,8 +3710,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B17" s="4">
@@ -2827,8 +3793,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="4">
@@ -2910,8 +3876,8 @@
         <v>600000.0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B19" s="4">
@@ -2993,8 +3959,8 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B20" s="4">
@@ -3076,8 +4042,8 @@
         <v>250000.0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="4">
@@ -3159,6 +4125,985 @@
         <v>250000.0</v>
       </c>
     </row>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3169,13 +5114,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.25"/>
     <col customWidth="1" min="2" max="27" width="7.13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3258,8 +5203,8 @@
         <v>130000.0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="4">
@@ -3341,8 +5286,8 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="4">
@@ -3424,8 +5369,8 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="4">
@@ -3507,8 +5452,8 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="4">
@@ -3590,8 +5535,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="4">
@@ -3673,8 +5618,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="4">
@@ -3756,8 +5701,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="4">
@@ -3839,8 +5784,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="4">
@@ -3922,8 +5867,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="4">
@@ -4005,8 +5950,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="4">
@@ -4088,8 +6033,8 @@
         <v>230000.0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="4">
@@ -4171,8 +6116,8 @@
         <v>230000.0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B13" s="4">
@@ -4254,8 +6199,8 @@
         <v>230000.0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="4">
@@ -4337,8 +6282,8 @@
         <v>700000.0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="4">
@@ -4420,8 +6365,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="4">
@@ -4503,8 +6448,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B17" s="4">
@@ -4586,8 +6531,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B18" s="4">
@@ -4669,8 +6614,8 @@
         <v>500000.0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B19" s="4">
@@ -4752,8 +6697,8 @@
         <v>0.0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B20" s="4">
@@ -4835,8 +6780,8 @@
         <v>230000.0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="4">
@@ -4918,6 +6863,985 @@
         <v>319000.0</v>
       </c>
     </row>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -18,40 +18,40 @@
     <t>모델명</t>
   </si>
   <si>
-    <t>KT_기변_닷컴</t>
+    <t>KT기변_닷컴</t>
   </si>
   <si>
-    <t>KT_기변_갤캠스</t>
+    <t>KT기변_갤캠</t>
   </si>
   <si>
-    <t>KT_번이_닷컴</t>
+    <t>KT번이_닷컴</t>
   </si>
   <si>
-    <t>KT_번이_갤캠스</t>
+    <t>KT번이_갤캠</t>
   </si>
   <si>
-    <t>U_기변_닷컴_고가</t>
+    <t>U+기변_닷컴(고)</t>
   </si>
   <si>
-    <t>U_기변_닷컴_저가</t>
+    <t>U+기변_닷컴(저)</t>
   </si>
   <si>
-    <t>U_기변_갤캠스_고가</t>
+    <t>U+기변_갤캠(고)</t>
   </si>
   <si>
-    <t>U_기변_갤캠스_저가</t>
+    <t>U+기변_갤캠(저)</t>
   </si>
   <si>
-    <t>U_번이_닷컴_고가</t>
+    <t>U+번이_닷컴(고)</t>
   </si>
   <si>
-    <t>U_번이_닷컴_저가</t>
+    <t>U+번이_닷컴(저)</t>
   </si>
   <si>
-    <t>U_번이_갤캠스_고가</t>
+    <t>U+번이_갤캠(고)</t>
   </si>
   <si>
-    <t>U_번이_갤캠스_저가</t>
+    <t>U+번이_갤캠(저)</t>
   </si>
   <si>
     <t>Z Fold8 Ultra 512G</t>
@@ -390,54 +390,48 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.25"/>
-    <col customWidth="1" min="2" max="2" width="12.13"/>
-    <col customWidth="1" min="3" max="3" width="13.75"/>
-    <col customWidth="1" min="4" max="4" width="12.13"/>
-    <col customWidth="1" min="5" max="5" width="13.75"/>
-    <col customWidth="1" min="6" max="7" width="15.5"/>
-    <col customWidth="1" min="8" max="9" width="17.13"/>
-    <col customWidth="1" min="10" max="11" width="15.5"/>
-    <col customWidth="1" min="12" max="13" width="17.13"/>
+    <col customWidth="1" min="2" max="5" width="11.13"/>
+    <col customWidth="1" min="6" max="13" width="14.13"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1"/>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="34">
   <si>
     <t>모델명</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>S25 Edge 256G</t>
+  </si>
+  <si>
+    <t>S26 FE</t>
   </si>
   <si>
     <t>S25 FE</t>
@@ -987,40 +990,40 @@
         <v>26</v>
       </c>
       <c r="B15" s="1">
-        <v>320000.0</v>
+        <v>0.0</v>
       </c>
       <c r="C15" s="1">
-        <v>445900.0</v>
+        <v>0.0</v>
       </c>
       <c r="D15" s="1">
-        <v>320000.0</v>
+        <v>0.0</v>
       </c>
       <c r="E15" s="1">
-        <v>445900.0</v>
+        <v>0.0</v>
       </c>
       <c r="F15" s="1">
-        <v>30000.0</v>
+        <v>0.0</v>
       </c>
       <c r="G15" s="1">
-        <v>30000.0</v>
+        <v>0.0</v>
       </c>
       <c r="H15" s="1">
-        <v>330000.0</v>
+        <v>0.0</v>
       </c>
       <c r="I15" s="1">
-        <v>50000.0</v>
+        <v>0.0</v>
       </c>
       <c r="J15" s="1">
-        <v>150000.0</v>
+        <v>0.0</v>
       </c>
       <c r="K15" s="1">
-        <v>30000.0</v>
+        <v>0.0</v>
       </c>
       <c r="L15" s="1">
-        <v>330000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M15" s="1">
-        <v>50000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N15" s="1"/>
     </row>
@@ -1029,37 +1032,37 @@
         <v>27</v>
       </c>
       <c r="B16" s="1">
-        <v>390000.0</v>
+        <v>320000.0</v>
       </c>
       <c r="C16" s="1">
-        <v>500000.0</v>
+        <v>445900.0</v>
       </c>
       <c r="D16" s="1">
-        <v>390000.0</v>
+        <v>320000.0</v>
       </c>
       <c r="E16" s="1">
-        <v>500000.0</v>
+        <v>445900.0</v>
       </c>
       <c r="F16" s="1">
-        <v>400000.0</v>
+        <v>30000.0</v>
       </c>
       <c r="G16" s="1">
         <v>30000.0</v>
       </c>
       <c r="H16" s="1">
-        <v>450000.0</v>
+        <v>330000.0</v>
       </c>
       <c r="I16" s="1">
         <v>50000.0</v>
       </c>
       <c r="J16" s="1">
-        <v>450000.0</v>
+        <v>150000.0</v>
       </c>
       <c r="K16" s="1">
         <v>30000.0</v>
       </c>
       <c r="L16" s="1">
-        <v>500000.0</v>
+        <v>330000.0</v>
       </c>
       <c r="M16" s="1">
         <v>50000.0</v>
@@ -1113,40 +1116,40 @@
         <v>29</v>
       </c>
       <c r="B18" s="1">
-        <v>0.0</v>
+        <v>390000.0</v>
       </c>
       <c r="C18" s="1">
-        <v>0.0</v>
+        <v>500000.0</v>
       </c>
       <c r="D18" s="1">
-        <v>0.0</v>
+        <v>390000.0</v>
       </c>
       <c r="E18" s="1">
-        <v>0.0</v>
+        <v>500000.0</v>
       </c>
       <c r="F18" s="1">
-        <v>0.0</v>
+        <v>400000.0</v>
       </c>
       <c r="G18" s="1">
-        <v>0.0</v>
+        <v>30000.0</v>
       </c>
       <c r="H18" s="1">
-        <v>0.0</v>
+        <v>450000.0</v>
       </c>
       <c r="I18" s="1">
-        <v>0.0</v>
+        <v>50000.0</v>
       </c>
       <c r="J18" s="1">
-        <v>0.0</v>
+        <v>450000.0</v>
       </c>
       <c r="K18" s="1">
-        <v>0.0</v>
+        <v>30000.0</v>
       </c>
       <c r="L18" s="1">
-        <v>0.0</v>
+        <v>500000.0</v>
       </c>
       <c r="M18" s="1">
-        <v>0.0</v>
+        <v>50000.0</v>
       </c>
       <c r="N18" s="1"/>
     </row>
@@ -1167,28 +1170,28 @@
         <v>0.0</v>
       </c>
       <c r="F19" s="1">
-        <v>30000.0</v>
+        <v>0.0</v>
       </c>
       <c r="G19" s="1">
-        <v>30000.0</v>
+        <v>0.0</v>
       </c>
       <c r="H19" s="1">
-        <v>30000.0</v>
+        <v>0.0</v>
       </c>
       <c r="I19" s="1">
-        <v>30000.0</v>
+        <v>0.0</v>
       </c>
       <c r="J19" s="1">
-        <v>100000.0</v>
+        <v>0.0</v>
       </c>
       <c r="K19" s="1">
-        <v>100000.0</v>
+        <v>0.0</v>
       </c>
       <c r="L19" s="1">
-        <v>100000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M19" s="1">
-        <v>100000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N19" s="1"/>
     </row>
@@ -1263,33 +1266,59 @@
         <v>30000.0</v>
       </c>
       <c r="J21" s="1">
-        <v>30000.0</v>
+        <v>100000.0</v>
       </c>
       <c r="K21" s="1">
-        <v>30000.0</v>
+        <v>100000.0</v>
       </c>
       <c r="L21" s="1">
-        <v>30000.0</v>
+        <v>100000.0</v>
       </c>
       <c r="M21" s="1">
-        <v>30000.0</v>
+        <v>100000.0</v>
       </c>
       <c r="N21" s="1"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
+      <c r="A22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>30000.0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>30000.0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>30000.0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>30000.0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>30000.0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>30000.0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>30000.0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>30000.0</v>
+      </c>
       <c r="N22" s="1"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -1388,7 +1417,22 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+    </row>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -2360,6 +2404,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3543,82 +3588,82 @@
         <v>26</v>
       </c>
       <c r="B15" s="4">
-        <v>115000.0</v>
+        <v>0.0</v>
       </c>
       <c r="C15" s="4">
-        <v>133000.0</v>
+        <v>0.0</v>
       </c>
       <c r="D15" s="4">
-        <v>151000.0</v>
+        <v>0.0</v>
       </c>
       <c r="E15" s="4">
-        <v>183000.0</v>
+        <v>0.0</v>
       </c>
       <c r="F15" s="4">
-        <v>210000.0</v>
+        <v>0.0</v>
       </c>
       <c r="G15" s="4">
-        <v>228000.0</v>
+        <v>0.0</v>
       </c>
       <c r="H15" s="4">
-        <v>233000.0</v>
+        <v>0.0</v>
       </c>
       <c r="I15" s="4">
-        <v>237000.0</v>
+        <v>0.0</v>
       </c>
       <c r="J15" s="4">
-        <v>255000.0</v>
+        <v>0.0</v>
       </c>
       <c r="K15" s="4">
-        <v>260000.0</v>
+        <v>0.0</v>
       </c>
       <c r="L15" s="4">
-        <v>269000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M15" s="4">
-        <v>273000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N15" s="4">
-        <v>300000.0</v>
+        <v>0.0</v>
       </c>
       <c r="O15" s="4">
-        <v>319000.0</v>
+        <v>0.0</v>
       </c>
       <c r="P15" s="4">
-        <v>332000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q15" s="4">
-        <v>346000.0</v>
+        <v>0.0</v>
       </c>
       <c r="R15" s="4">
-        <v>355000.0</v>
+        <v>0.0</v>
       </c>
       <c r="S15" s="4">
-        <v>364000.0</v>
+        <v>0.0</v>
       </c>
       <c r="T15" s="4">
-        <v>500000.0</v>
+        <v>0.0</v>
       </c>
       <c r="U15" s="4">
-        <v>500000.0</v>
+        <v>0.0</v>
       </c>
       <c r="V15" s="4">
-        <v>500000.0</v>
+        <v>0.0</v>
       </c>
       <c r="W15" s="4">
-        <v>500000.0</v>
+        <v>0.0</v>
       </c>
       <c r="X15" s="4">
-        <v>500000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y15" s="4">
-        <v>500000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z15" s="4">
-        <v>500000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA15" s="4">
-        <v>500000.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
@@ -3680,13 +3725,13 @@
         <v>364000.0</v>
       </c>
       <c r="T16" s="4">
-        <v>377000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="U16" s="4">
-        <v>413000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="V16" s="4">
-        <v>450000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="W16" s="4">
         <v>500000.0</v>
@@ -3727,7 +3772,7 @@
         <v>228000.0</v>
       </c>
       <c r="H17" s="4">
-        <v>228000.0</v>
+        <v>233000.0</v>
       </c>
       <c r="I17" s="4">
         <v>237000.0</v>
@@ -3792,82 +3837,82 @@
         <v>29</v>
       </c>
       <c r="B18" s="4">
-        <v>55000.0</v>
+        <v>115000.0</v>
       </c>
       <c r="C18" s="4">
-        <v>82000.0</v>
+        <v>133000.0</v>
       </c>
       <c r="D18" s="4">
-        <v>109000.0</v>
+        <v>151000.0</v>
       </c>
       <c r="E18" s="4">
-        <v>156000.0</v>
+        <v>183000.0</v>
       </c>
       <c r="F18" s="4">
-        <v>196000.0</v>
+        <v>210000.0</v>
       </c>
       <c r="G18" s="4">
-        <v>223000.0</v>
+        <v>228000.0</v>
       </c>
       <c r="H18" s="4">
-        <v>230000.0</v>
+        <v>228000.0</v>
       </c>
       <c r="I18" s="4">
-        <v>236000.0</v>
+        <v>237000.0</v>
       </c>
       <c r="J18" s="4">
-        <v>263000.0</v>
+        <v>255000.0</v>
       </c>
       <c r="K18" s="4">
-        <v>270000.0</v>
+        <v>260000.0</v>
       </c>
       <c r="L18" s="4">
-        <v>283000.0</v>
+        <v>269000.0</v>
       </c>
       <c r="M18" s="4">
-        <v>290000.0</v>
+        <v>273000.0</v>
       </c>
       <c r="N18" s="4">
-        <v>330000.0</v>
+        <v>300000.0</v>
       </c>
       <c r="O18" s="4">
-        <v>357000.0</v>
+        <v>319000.0</v>
       </c>
       <c r="P18" s="4">
+        <v>332000.0</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>346000.0</v>
+      </c>
+      <c r="R18" s="4">
+        <v>355000.0</v>
+      </c>
+      <c r="S18" s="4">
+        <v>364000.0</v>
+      </c>
+      <c r="T18" s="4">
         <v>377000.0</v>
       </c>
-      <c r="Q18" s="4">
-        <v>398000.0</v>
-      </c>
-      <c r="R18" s="4">
-        <v>411000.0</v>
-      </c>
-      <c r="S18" s="4">
-        <v>425000.0</v>
-      </c>
-      <c r="T18" s="4">
-        <v>445000.0</v>
-      </c>
       <c r="U18" s="4">
-        <v>498000.0</v>
+        <v>413000.0</v>
       </c>
       <c r="V18" s="4">
-        <v>530000.0</v>
+        <v>450000.0</v>
       </c>
       <c r="W18" s="4">
-        <v>600000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="X18" s="4">
-        <v>600000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="Y18" s="4">
-        <v>600000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="Z18" s="4">
-        <v>600000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="AA18" s="4">
-        <v>600000.0</v>
+        <v>500000.0</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
@@ -3875,82 +3920,82 @@
         <v>30</v>
       </c>
       <c r="B19" s="4">
-        <v>0.0</v>
+        <v>55000.0</v>
       </c>
       <c r="C19" s="4">
-        <v>0.0</v>
+        <v>82000.0</v>
       </c>
       <c r="D19" s="4">
-        <v>0.0</v>
+        <v>109000.0</v>
       </c>
       <c r="E19" s="4">
-        <v>0.0</v>
+        <v>156000.0</v>
       </c>
       <c r="F19" s="4">
-        <v>0.0</v>
+        <v>196000.0</v>
       </c>
       <c r="G19" s="4">
-        <v>0.0</v>
+        <v>223000.0</v>
       </c>
       <c r="H19" s="4">
-        <v>0.0</v>
+        <v>230000.0</v>
       </c>
       <c r="I19" s="4">
-        <v>0.0</v>
+        <v>236000.0</v>
       </c>
       <c r="J19" s="4">
-        <v>0.0</v>
+        <v>263000.0</v>
       </c>
       <c r="K19" s="4">
-        <v>0.0</v>
+        <v>270000.0</v>
       </c>
       <c r="L19" s="4">
-        <v>0.0</v>
+        <v>283000.0</v>
       </c>
       <c r="M19" s="4">
-        <v>0.0</v>
+        <v>290000.0</v>
       </c>
       <c r="N19" s="4">
-        <v>0.0</v>
+        <v>330000.0</v>
       </c>
       <c r="O19" s="4">
-        <v>0.0</v>
+        <v>357000.0</v>
       </c>
       <c r="P19" s="4">
-        <v>0.0</v>
+        <v>377000.0</v>
       </c>
       <c r="Q19" s="4">
-        <v>0.0</v>
+        <v>398000.0</v>
       </c>
       <c r="R19" s="4">
-        <v>0.0</v>
+        <v>411000.0</v>
       </c>
       <c r="S19" s="4">
-        <v>0.0</v>
+        <v>425000.0</v>
       </c>
       <c r="T19" s="4">
-        <v>0.0</v>
+        <v>445000.0</v>
       </c>
       <c r="U19" s="4">
-        <v>0.0</v>
+        <v>498000.0</v>
       </c>
       <c r="V19" s="4">
-        <v>0.0</v>
+        <v>530000.0</v>
       </c>
       <c r="W19" s="4">
-        <v>0.0</v>
+        <v>600000.0</v>
       </c>
       <c r="X19" s="4">
-        <v>0.0</v>
+        <v>600000.0</v>
       </c>
       <c r="Y19" s="4">
-        <v>0.0</v>
+        <v>600000.0</v>
       </c>
       <c r="Z19" s="4">
-        <v>0.0</v>
+        <v>600000.0</v>
       </c>
       <c r="AA19" s="4">
-        <v>0.0</v>
+        <v>600000.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -3958,82 +4003,82 @@
         <v>31</v>
       </c>
       <c r="B20" s="4">
-        <v>36000.0</v>
+        <v>0.0</v>
       </c>
       <c r="C20" s="4">
-        <v>42000.0</v>
+        <v>0.0</v>
       </c>
       <c r="D20" s="4">
-        <v>49000.0</v>
+        <v>0.0</v>
       </c>
       <c r="E20" s="4">
-        <v>60000.0</v>
+        <v>0.0</v>
       </c>
       <c r="F20" s="4">
-        <v>69000.0</v>
+        <v>0.0</v>
       </c>
       <c r="G20" s="4">
-        <v>75000.0</v>
+        <v>0.0</v>
       </c>
       <c r="H20" s="4">
-        <v>77000.0</v>
+        <v>0.0</v>
       </c>
       <c r="I20" s="4">
-        <v>78000.0</v>
+        <v>0.0</v>
       </c>
       <c r="J20" s="4">
-        <v>85000.0</v>
+        <v>0.0</v>
       </c>
       <c r="K20" s="4">
-        <v>86000.0</v>
+        <v>0.0</v>
       </c>
       <c r="L20" s="4">
-        <v>89000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M20" s="4">
-        <v>91000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N20" s="4">
-        <v>100000.0</v>
+        <v>0.0</v>
       </c>
       <c r="O20" s="4">
-        <v>107000.0</v>
+        <v>0.0</v>
       </c>
       <c r="P20" s="4">
-        <v>111000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q20" s="4">
-        <v>116000.0</v>
+        <v>0.0</v>
       </c>
       <c r="R20" s="4">
-        <v>119000.0</v>
+        <v>0.0</v>
       </c>
       <c r="S20" s="4">
-        <v>122000.0</v>
+        <v>0.0</v>
       </c>
       <c r="T20" s="4">
-        <v>127000.0</v>
+        <v>0.0</v>
       </c>
       <c r="U20" s="4">
-        <v>137000.0</v>
+        <v>0.0</v>
       </c>
       <c r="V20" s="4">
-        <v>147000.0</v>
+        <v>0.0</v>
       </c>
       <c r="W20" s="4">
-        <v>150000.0</v>
+        <v>0.0</v>
       </c>
       <c r="X20" s="4">
-        <v>183000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y20" s="4">
-        <v>201000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z20" s="4">
-        <v>221000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA20" s="4">
-        <v>250000.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -4098,7 +4143,7 @@
         <v>127000.0</v>
       </c>
       <c r="U21" s="4">
-        <v>139000.0</v>
+        <v>137000.0</v>
       </c>
       <c r="V21" s="4">
         <v>147000.0</v>
@@ -4119,7 +4164,89 @@
         <v>250000.0</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="4">
+        <v>36000.0</v>
+      </c>
+      <c r="C22" s="4">
+        <v>42000.0</v>
+      </c>
+      <c r="D22" s="4">
+        <v>49000.0</v>
+      </c>
+      <c r="E22" s="4">
+        <v>60000.0</v>
+      </c>
+      <c r="F22" s="4">
+        <v>69000.0</v>
+      </c>
+      <c r="G22" s="4">
+        <v>75000.0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>77000.0</v>
+      </c>
+      <c r="I22" s="4">
+        <v>78000.0</v>
+      </c>
+      <c r="J22" s="4">
+        <v>85000.0</v>
+      </c>
+      <c r="K22" s="4">
+        <v>86000.0</v>
+      </c>
+      <c r="L22" s="4">
+        <v>89000.0</v>
+      </c>
+      <c r="M22" s="4">
+        <v>91000.0</v>
+      </c>
+      <c r="N22" s="4">
+        <v>100000.0</v>
+      </c>
+      <c r="O22" s="4">
+        <v>107000.0</v>
+      </c>
+      <c r="P22" s="4">
+        <v>111000.0</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>116000.0</v>
+      </c>
+      <c r="R22" s="4">
+        <v>119000.0</v>
+      </c>
+      <c r="S22" s="4">
+        <v>122000.0</v>
+      </c>
+      <c r="T22" s="4">
+        <v>127000.0</v>
+      </c>
+      <c r="U22" s="4">
+        <v>139000.0</v>
+      </c>
+      <c r="V22" s="4">
+        <v>147000.0</v>
+      </c>
+      <c r="W22" s="4">
+        <v>150000.0</v>
+      </c>
+      <c r="X22" s="4">
+        <v>183000.0</v>
+      </c>
+      <c r="Y22" s="4">
+        <v>201000.0</v>
+      </c>
+      <c r="Z22" s="4">
+        <v>221000.0</v>
+      </c>
+      <c r="AA22" s="4">
+        <v>250000.0</v>
+      </c>
+    </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1"/>
@@ -5098,6 +5225,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -6287,76 +6415,76 @@
         <v>0.0</v>
       </c>
       <c r="D15" s="4">
-        <v>175000.0</v>
+        <v>0.0</v>
       </c>
       <c r="E15" s="4">
-        <v>198000.0</v>
+        <v>0.0</v>
       </c>
       <c r="F15" s="4">
-        <v>222000.0</v>
+        <v>0.0</v>
       </c>
       <c r="G15" s="4">
-        <v>233000.0</v>
+        <v>0.0</v>
       </c>
       <c r="H15" s="4">
-        <v>257000.0</v>
+        <v>0.0</v>
       </c>
       <c r="I15" s="4">
-        <v>262000.0</v>
+        <v>0.0</v>
       </c>
       <c r="J15" s="4">
-        <v>268000.0</v>
+        <v>0.0</v>
       </c>
       <c r="K15" s="4">
-        <v>280000.0</v>
+        <v>0.0</v>
       </c>
       <c r="L15" s="4">
         <v>0.0</v>
       </c>
       <c r="M15" s="4">
-        <v>326000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N15" s="4">
-        <v>350000.0</v>
+        <v>0.0</v>
       </c>
       <c r="O15" s="4">
-        <v>361000.0</v>
+        <v>0.0</v>
       </c>
       <c r="P15" s="4">
-        <v>373000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q15" s="4">
-        <v>390000.0</v>
+        <v>0.0</v>
       </c>
       <c r="R15" s="4">
-        <v>402000.0</v>
+        <v>0.0</v>
       </c>
       <c r="S15" s="4">
-        <v>407000.0</v>
+        <v>0.0</v>
       </c>
       <c r="T15" s="4">
-        <v>414000.0</v>
+        <v>0.0</v>
       </c>
       <c r="U15" s="4">
-        <v>442000.0</v>
+        <v>0.0</v>
       </c>
       <c r="V15" s="4">
-        <v>460000.0</v>
+        <v>0.0</v>
       </c>
       <c r="W15" s="4">
-        <v>500000.0</v>
+        <v>0.0</v>
       </c>
       <c r="X15" s="4">
-        <v>500000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y15" s="4">
-        <v>500000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z15" s="4">
-        <v>500000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA15" s="4">
-        <v>500000.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
@@ -6394,7 +6522,7 @@
         <v>280000.0</v>
       </c>
       <c r="L16" s="4">
-        <v>291000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M16" s="4">
         <v>326000.0</v>
@@ -6474,7 +6602,7 @@
         <v>268000.0</v>
       </c>
       <c r="K17" s="4">
-        <v>288000.0</v>
+        <v>280000.0</v>
       </c>
       <c r="L17" s="4">
         <v>291000.0</v>
@@ -6557,7 +6685,7 @@
         <v>268000.0</v>
       </c>
       <c r="K18" s="4">
-        <v>280000.0</v>
+        <v>288000.0</v>
       </c>
       <c r="L18" s="4">
         <v>291000.0</v>
@@ -6619,76 +6747,76 @@
         <v>0.0</v>
       </c>
       <c r="D19" s="4">
-        <v>0.0</v>
+        <v>175000.0</v>
       </c>
       <c r="E19" s="4">
-        <v>0.0</v>
+        <v>198000.0</v>
       </c>
       <c r="F19" s="4">
-        <v>0.0</v>
+        <v>222000.0</v>
       </c>
       <c r="G19" s="4">
-        <v>0.0</v>
+        <v>233000.0</v>
       </c>
       <c r="H19" s="4">
-        <v>0.0</v>
+        <v>257000.0</v>
       </c>
       <c r="I19" s="4">
-        <v>0.0</v>
+        <v>262000.0</v>
       </c>
       <c r="J19" s="4">
-        <v>0.0</v>
+        <v>268000.0</v>
       </c>
       <c r="K19" s="4">
-        <v>0.0</v>
+        <v>280000.0</v>
       </c>
       <c r="L19" s="4">
-        <v>0.0</v>
+        <v>291000.0</v>
       </c>
       <c r="M19" s="4">
-        <v>0.0</v>
+        <v>326000.0</v>
       </c>
       <c r="N19" s="4">
-        <v>0.0</v>
+        <v>350000.0</v>
       </c>
       <c r="O19" s="4">
-        <v>0.0</v>
+        <v>361000.0</v>
       </c>
       <c r="P19" s="4">
-        <v>0.0</v>
+        <v>373000.0</v>
       </c>
       <c r="Q19" s="4">
-        <v>0.0</v>
+        <v>390000.0</v>
       </c>
       <c r="R19" s="4">
-        <v>0.0</v>
+        <v>402000.0</v>
       </c>
       <c r="S19" s="4">
-        <v>0.0</v>
+        <v>407000.0</v>
       </c>
       <c r="T19" s="4">
-        <v>0.0</v>
+        <v>414000.0</v>
       </c>
       <c r="U19" s="4">
-        <v>0.0</v>
+        <v>442000.0</v>
       </c>
       <c r="V19" s="4">
-        <v>0.0</v>
+        <v>460000.0</v>
       </c>
       <c r="W19" s="4">
-        <v>0.0</v>
+        <v>500000.0</v>
       </c>
       <c r="X19" s="4">
-        <v>0.0</v>
+        <v>500000.0</v>
       </c>
       <c r="Y19" s="4">
-        <v>0.0</v>
+        <v>500000.0</v>
       </c>
       <c r="Z19" s="4">
-        <v>0.0</v>
+        <v>500000.0</v>
       </c>
       <c r="AA19" s="4">
-        <v>0.0</v>
+        <v>500000.0</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
@@ -6702,76 +6830,76 @@
         <v>0.0</v>
       </c>
       <c r="D20" s="4">
-        <v>52000.0</v>
+        <v>0.0</v>
       </c>
       <c r="E20" s="4">
-        <v>59000.0</v>
+        <v>0.0</v>
       </c>
       <c r="F20" s="4">
-        <v>66000.0</v>
+        <v>0.0</v>
       </c>
       <c r="G20" s="4">
-        <v>69000.0</v>
+        <v>0.0</v>
       </c>
       <c r="H20" s="4">
-        <v>76000.0</v>
+        <v>0.0</v>
       </c>
       <c r="I20" s="4">
-        <v>78000.0</v>
+        <v>0.0</v>
       </c>
       <c r="J20" s="4">
-        <v>80000.0</v>
+        <v>0.0</v>
       </c>
       <c r="K20" s="4">
-        <v>84000.0</v>
+        <v>0.0</v>
       </c>
       <c r="L20" s="4">
-        <v>87000.0</v>
+        <v>0.0</v>
       </c>
       <c r="M20" s="4">
-        <v>98000.0</v>
+        <v>0.0</v>
       </c>
       <c r="N20" s="4">
-        <v>105000.0</v>
+        <v>0.0</v>
       </c>
       <c r="O20" s="4">
-        <v>108000.0</v>
+        <v>0.0</v>
       </c>
       <c r="P20" s="4">
-        <v>112000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q20" s="4">
-        <v>117000.0</v>
+        <v>0.0</v>
       </c>
       <c r="R20" s="4">
-        <v>121000.0</v>
+        <v>0.0</v>
       </c>
       <c r="S20" s="4">
-        <v>122000.0</v>
+        <v>0.0</v>
       </c>
       <c r="T20" s="4">
-        <v>124000.0</v>
+        <v>0.0</v>
       </c>
       <c r="U20" s="4">
-        <v>133000.0</v>
+        <v>0.0</v>
       </c>
       <c r="V20" s="4">
-        <v>138000.0</v>
+        <v>0.0</v>
       </c>
       <c r="W20" s="4">
-        <v>151000.0</v>
+        <v>0.0</v>
       </c>
       <c r="X20" s="4">
-        <v>168000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Y20" s="4">
-        <v>186000.0</v>
+        <v>0.0</v>
       </c>
       <c r="Z20" s="4">
-        <v>204000.0</v>
+        <v>0.0</v>
       </c>
       <c r="AA20" s="4">
-        <v>230000.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -6779,85 +6907,167 @@
         <v>32</v>
       </c>
       <c r="B21" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D21" s="4">
+        <v>52000.0</v>
+      </c>
+      <c r="E21" s="4">
+        <v>59000.0</v>
+      </c>
+      <c r="F21" s="4">
+        <v>66000.0</v>
+      </c>
+      <c r="G21" s="4">
+        <v>69000.0</v>
+      </c>
+      <c r="H21" s="4">
+        <v>76000.0</v>
+      </c>
+      <c r="I21" s="4">
+        <v>78000.0</v>
+      </c>
+      <c r="J21" s="4">
+        <v>80000.0</v>
+      </c>
+      <c r="K21" s="4">
+        <v>84000.0</v>
+      </c>
+      <c r="L21" s="4">
+        <v>87000.0</v>
+      </c>
+      <c r="M21" s="4">
+        <v>98000.0</v>
+      </c>
+      <c r="N21" s="4">
+        <v>105000.0</v>
+      </c>
+      <c r="O21" s="4">
+        <v>108000.0</v>
+      </c>
+      <c r="P21" s="4">
+        <v>112000.0</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>117000.0</v>
+      </c>
+      <c r="R21" s="4">
+        <v>121000.0</v>
+      </c>
+      <c r="S21" s="4">
+        <v>122000.0</v>
+      </c>
+      <c r="T21" s="4">
         <v>124000.0</v>
       </c>
-      <c r="C21" s="4">
+      <c r="U21" s="4">
+        <v>133000.0</v>
+      </c>
+      <c r="V21" s="4">
+        <v>138000.0</v>
+      </c>
+      <c r="W21" s="4">
+        <v>151000.0</v>
+      </c>
+      <c r="X21" s="4">
+        <v>168000.0</v>
+      </c>
+      <c r="Y21" s="4">
+        <v>186000.0</v>
+      </c>
+      <c r="Z21" s="4">
+        <v>204000.0</v>
+      </c>
+      <c r="AA21" s="4">
+        <v>230000.0</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="4">
+        <v>124000.0</v>
+      </c>
+      <c r="C22" s="4">
         <v>139000.0</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D22" s="4">
         <v>141000.0</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E22" s="4">
         <v>151000.0</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F22" s="4">
         <v>161000.0</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G22" s="4">
         <v>277000.0</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H22" s="4">
         <v>298000.0</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I22" s="4">
         <v>303000.0</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J22" s="4">
         <v>308000.0</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="L21" s="4">
+      <c r="L22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="M21" s="4">
+      <c r="M22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="N21" s="4">
+      <c r="N22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="O21" s="4">
+      <c r="O22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="P21" s="4">
+      <c r="P22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="Q22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="R21" s="4">
+      <c r="R22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="S21" s="4">
+      <c r="S22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="T21" s="4">
+      <c r="T22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="U21" s="4">
+      <c r="U22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="V21" s="4">
+      <c r="V22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="W21" s="4">
+      <c r="W22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="X21" s="4">
+      <c r="X22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="Y21" s="4">
+      <c r="Y22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="Z21" s="4">
+      <c r="Z22" s="4">
         <v>319000.0</v>
       </c>
-      <c r="AA21" s="4">
+      <c r="AA22" s="4">
         <v>319000.0</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1"/>
@@ -7836,6 +8046,7 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -614,14 +614,14 @@
       <c r="B6" s="1">
         <v>360000.0</v>
       </c>
-      <c r="C6" s="1">
-        <v>360000.0</v>
+      <c r="C6" s="2">
+        <v>460000.0</v>
       </c>
       <c r="D6" s="1">
         <v>360000.0</v>
       </c>
-      <c r="E6" s="1">
-        <v>360000.0</v>
+      <c r="E6" s="2">
+        <v>460000.0</v>
       </c>
       <c r="F6" s="1">
         <v>260000.0</v>
@@ -656,14 +656,14 @@
       <c r="B7" s="1">
         <v>360000.0</v>
       </c>
-      <c r="C7" s="1">
-        <v>360000.0</v>
+      <c r="C7" s="2">
+        <v>460000.0</v>
       </c>
       <c r="D7" s="1">
         <v>360000.0</v>
       </c>
-      <c r="E7" s="1">
-        <v>360000.0</v>
+      <c r="E7" s="2">
+        <v>460000.0</v>
       </c>
       <c r="F7" s="1">
         <v>260000.0</v>
@@ -698,14 +698,14 @@
       <c r="B8" s="1">
         <v>460000.0</v>
       </c>
-      <c r="C8" s="1">
-        <v>460000.0</v>
+      <c r="C8" s="2">
+        <v>360000.0</v>
       </c>
       <c r="D8" s="1">
         <v>460000.0</v>
       </c>
-      <c r="E8" s="1">
-        <v>460000.0</v>
+      <c r="E8" s="2">
+        <v>360000.0</v>
       </c>
       <c r="F8" s="1">
         <v>360000.0</v>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -135,11 +135,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -6145,7 +6147,7 @@
         <v>133000</v>
       </c>
       <c r="V11" s="4">
-        <v>0</v>
+        <v>138000</v>
       </c>
       <c r="W11" s="4">
         <v>151000</v>
@@ -6228,7 +6230,7 @@
         <v>133000</v>
       </c>
       <c r="V12" s="4">
-        <v>0</v>
+        <v>138000</v>
       </c>
       <c r="W12" s="4">
         <v>151000</v>
@@ -6311,7 +6313,7 @@
         <v>133000</v>
       </c>
       <c r="V13" s="4">
-        <v>0</v>
+        <v>138000</v>
       </c>
       <c r="W13" s="4">
         <v>151000</v>
@@ -6847,22 +6849,22 @@
         <v>202000</v>
       </c>
       <c r="G20" s="4">
-        <v>0</v>
+        <v>213000</v>
       </c>
       <c r="H20" s="4">
-        <v>0</v>
+        <v>235000</v>
       </c>
       <c r="I20" s="4">
-        <v>0</v>
+        <v>240000</v>
       </c>
       <c r="J20" s="4">
-        <v>0</v>
+        <v>245000</v>
       </c>
       <c r="K20" s="4">
         <v>257000</v>
       </c>
       <c r="L20" s="4">
-        <v>0</v>
+        <v>267000</v>
       </c>
       <c r="M20" s="4">
         <v>300000</v>
@@ -6883,7 +6885,7 @@
         <v>358000</v>
       </c>
       <c r="S20" s="4">
-        <v>0</v>
+        <v>363000</v>
       </c>
       <c r="T20" s="4">
         <v>369000</v>
@@ -6892,7 +6894,7 @@
         <v>395000</v>
       </c>
       <c r="V20" s="4">
-        <v>0</v>
+        <v>395000</v>
       </c>
       <c r="W20" s="4">
         <v>400000</v>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ETW\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BA3BA63-B8C9-4D47-8FB2-31732E81CEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452A53A9-D426-4039-8EBF-F99FC631CDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8850" yWindow="2700" windowWidth="22410" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8370" yWindow="3120" windowWidth="22410" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="추가지원금" sheetId="1" r:id="rId1"/>
@@ -960,7 +960,7 @@
         <v>460000</v>
       </c>
       <c r="F5" s="2">
-        <v>360000</v>
+        <v>400000</v>
       </c>
       <c r="G5" s="2">
         <v>30000</v>
@@ -972,7 +972,7 @@
         <v>30000</v>
       </c>
       <c r="J5" s="2">
-        <v>410000</v>
+        <v>450000</v>
       </c>
       <c r="K5" s="2">
         <v>50000</v>
@@ -1002,25 +1002,25 @@
         <v>460000</v>
       </c>
       <c r="F6" s="2">
-        <v>260000</v>
+        <v>300000</v>
       </c>
       <c r="G6" s="2">
         <v>30000</v>
       </c>
       <c r="H6" s="2">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="I6" s="2">
         <v>30000</v>
       </c>
       <c r="J6" s="2">
-        <v>310000</v>
+        <v>350000</v>
       </c>
       <c r="K6" s="2">
         <v>50000</v>
       </c>
       <c r="L6" s="2">
-        <v>410000</v>
+        <v>350000</v>
       </c>
       <c r="M6" s="2">
         <v>50000</v>
@@ -1044,25 +1044,25 @@
         <v>460000</v>
       </c>
       <c r="F7" s="2">
-        <v>260000</v>
+        <v>300000</v>
       </c>
       <c r="G7" s="2">
         <v>30000</v>
       </c>
       <c r="H7" s="2">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="I7" s="2">
         <v>30000</v>
       </c>
       <c r="J7" s="2">
-        <v>310000</v>
+        <v>350000</v>
       </c>
       <c r="K7" s="2">
         <v>50000</v>
       </c>
       <c r="L7" s="2">
-        <v>410000</v>
+        <v>350000</v>
       </c>
       <c r="M7" s="2">
         <v>50000</v>
@@ -1086,7 +1086,7 @@
         <v>360000</v>
       </c>
       <c r="F8" s="2">
-        <v>360000</v>
+        <v>400000</v>
       </c>
       <c r="G8" s="2">
         <v>30000</v>
@@ -1098,7 +1098,7 @@
         <v>30000</v>
       </c>
       <c r="J8" s="2">
-        <v>410000</v>
+        <v>450000</v>
       </c>
       <c r="K8" s="2">
         <v>50000</v>
@@ -1128,25 +1128,25 @@
         <v>360000</v>
       </c>
       <c r="F9" s="2">
-        <v>260000</v>
+        <v>300000</v>
       </c>
       <c r="G9" s="2">
         <v>30000</v>
       </c>
       <c r="H9" s="2">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="I9" s="2">
         <v>30000</v>
       </c>
       <c r="J9" s="2">
-        <v>310000</v>
+        <v>350000</v>
       </c>
       <c r="K9" s="2">
         <v>50000</v>
       </c>
       <c r="L9" s="2">
-        <v>410000</v>
+        <v>350000</v>
       </c>
       <c r="M9" s="2">
         <v>50000</v>
@@ -1170,25 +1170,25 @@
         <v>360000</v>
       </c>
       <c r="F10" s="2">
-        <v>260000</v>
+        <v>300000</v>
       </c>
       <c r="G10" s="2">
         <v>30000</v>
       </c>
       <c r="H10" s="2">
-        <v>360000</v>
+        <v>300000</v>
       </c>
       <c r="I10" s="2">
         <v>30000</v>
       </c>
       <c r="J10" s="2">
-        <v>310000</v>
+        <v>350000</v>
       </c>
       <c r="K10" s="2">
         <v>50000</v>
       </c>
       <c r="L10" s="2">
-        <v>410000</v>
+        <v>350000</v>
       </c>
       <c r="M10" s="2">
         <v>50000</v>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -1,22 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ETW\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452A53A9-D426-4039-8EBF-F99FC631CDCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8370" yWindow="3120" windowWidth="22410" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3684" yWindow="1800" windowWidth="22416" windowHeight="14556"/>
   </bookViews>
   <sheets>
     <sheet name="추가지원금" sheetId="1" r:id="rId1"/>
     <sheet name="KT_공통지원금" sheetId="2" r:id="rId2"/>
     <sheet name="U_공통지원금" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">추가지원금!$A$1:$M$22</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -483,7 +480,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -761,21 +758,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:N1001"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -817,7 +814,7 @@
       </c>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -859,7 +856,7 @@
       </c>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -901,7 +898,7 @@
       </c>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -943,7 +940,7 @@
       </c>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -985,7 +982,7 @@
       </c>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1027,7 +1024,7 @@
       </c>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1069,7 +1066,7 @@
       </c>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1111,7 +1108,7 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1153,7 +1150,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -1195,7 +1192,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1218,7 +1215,7 @@
         <v>30000</v>
       </c>
       <c r="H11" s="2">
-        <v>460000</v>
+        <v>280000</v>
       </c>
       <c r="I11" s="2">
         <v>30000</v>
@@ -1230,14 +1227,14 @@
         <v>50000</v>
       </c>
       <c r="L11" s="2">
-        <v>510000</v>
+        <v>330000</v>
       </c>
       <c r="M11" s="2">
         <v>50000</v>
       </c>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1260,7 +1257,7 @@
         <v>30000</v>
       </c>
       <c r="H12" s="2">
-        <v>460000</v>
+        <v>280000</v>
       </c>
       <c r="I12" s="2">
         <v>30000</v>
@@ -1272,14 +1269,14 @@
         <v>50000</v>
       </c>
       <c r="L12" s="2">
-        <v>510000</v>
+        <v>330000</v>
       </c>
       <c r="M12" s="2">
         <v>50000</v>
       </c>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1302,7 +1299,7 @@
         <v>30000</v>
       </c>
       <c r="H13" s="2">
-        <v>460000</v>
+        <v>280000</v>
       </c>
       <c r="I13" s="2">
         <v>30000</v>
@@ -1314,14 +1311,14 @@
         <v>50000</v>
       </c>
       <c r="L13" s="2">
-        <v>510000</v>
+        <v>330000</v>
       </c>
       <c r="M13" s="2">
         <v>50000</v>
       </c>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -1344,7 +1341,7 @@
         <v>30000</v>
       </c>
       <c r="H14" s="2">
-        <v>460000</v>
+        <v>280000</v>
       </c>
       <c r="I14" s="2">
         <v>30000</v>
@@ -1356,14 +1353,14 @@
         <v>50000</v>
       </c>
       <c r="L14" s="2">
-        <v>510000</v>
+        <v>330000</v>
       </c>
       <c r="M14" s="2">
         <v>50000</v>
       </c>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1405,7 +1402,7 @@
       </c>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -1434,20 +1431,20 @@
         <v>30000</v>
       </c>
       <c r="J16" s="2">
-        <v>330000</v>
+        <v>80000</v>
       </c>
       <c r="K16" s="2">
         <v>50000</v>
       </c>
       <c r="L16" s="2">
-        <v>330000</v>
+        <v>200000</v>
       </c>
       <c r="M16" s="2">
         <v>50000</v>
       </c>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -1464,32 +1461,32 @@
         <v>500000</v>
       </c>
       <c r="F17" s="2">
-        <v>400000</v>
+        <v>250000</v>
       </c>
       <c r="G17" s="2">
         <v>30000</v>
       </c>
       <c r="H17" s="2">
-        <v>450000</v>
+        <v>250000</v>
       </c>
       <c r="I17" s="2">
         <v>30000</v>
       </c>
       <c r="J17" s="2">
-        <v>450000</v>
+        <v>300000</v>
       </c>
       <c r="K17" s="2">
         <v>50000</v>
       </c>
       <c r="L17" s="2">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="M17" s="2">
         <v>50000</v>
       </c>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -1506,32 +1503,32 @@
         <v>500000</v>
       </c>
       <c r="F18" s="2">
-        <v>400000</v>
+        <v>250000</v>
       </c>
       <c r="G18" s="2">
         <v>30000</v>
       </c>
       <c r="H18" s="2">
-        <v>450000</v>
+        <v>250000</v>
       </c>
       <c r="I18" s="2">
         <v>30000</v>
       </c>
       <c r="J18" s="2">
-        <v>450000</v>
+        <v>300000</v>
       </c>
       <c r="K18" s="2">
         <v>50000</v>
       </c>
       <c r="L18" s="2">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="M18" s="2">
         <v>50000</v>
       </c>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -1573,7 +1570,7 @@
       </c>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -1615,7 +1612,7 @@
       </c>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -1657,7 +1654,7 @@
       </c>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -1699,7 +1696,7 @@
       </c>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1715,7 +1712,7 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1731,7 +1728,7 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1747,7 +1744,7 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1763,7 +1760,7 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1779,7 +1776,7 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1795,7 +1792,7 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1811,978 +1808,978 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2790,18 +2787,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1001"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2884,7 +2881,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2967,7 +2964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3050,7 +3047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -3133,7 +3130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -3216,7 +3213,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -3299,7 +3296,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -3382,7 +3379,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -3465,7 +3462,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -3548,7 +3545,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -3631,7 +3628,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3714,7 +3711,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -3797,7 +3794,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -3880,7 +3877,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -3963,7 +3960,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -4046,7 +4043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -4129,7 +4126,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -4212,7 +4209,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -4295,7 +4292,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -4378,7 +4375,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -4461,7 +4458,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -4544,7 +4541,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -4627,985 +4624,985 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5614,18 +5611,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1001"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5708,7 +5705,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -5791,7 +5788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -5874,7 +5871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -5957,7 +5954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -6040,7 +6037,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -6123,7 +6120,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -6206,7 +6203,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -6289,7 +6286,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -6372,7 +6369,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -6455,7 +6452,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -6538,7 +6535,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -6621,7 +6618,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -6704,7 +6701,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -6787,7 +6784,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -6870,7 +6867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -6953,7 +6950,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -7036,7 +7033,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -7119,7 +7116,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -7202,7 +7199,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -7285,7 +7282,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -7368,7 +7365,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -7451,985 +7448,985 @@
         <v>319000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61C6D5B3-61FE-CE49-9B28-8AA1CECD9208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3684" yWindow="1800" windowWidth="22416" windowHeight="14556"/>
+    <workbookView xWindow="3684" yWindow="1800" windowWidth="22416" windowHeight="14556" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="추가지원금" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">추가지원금!$A$1:$M$22</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -480,7 +494,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -758,21 +772,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:N1001"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.62890625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="12.5390625" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="16.31640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -814,7 +828,7 @@
       </c>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -856,7 +870,7 @@
       </c>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -898,7 +912,7 @@
       </c>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -940,7 +954,7 @@
       </c>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -982,7 +996,7 @@
       </c>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1024,7 +1038,7 @@
       </c>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1066,7 +1080,7 @@
       </c>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1108,7 +1122,7 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1150,7 +1164,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -1192,7 +1206,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1234,7 +1248,7 @@
       </c>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1276,7 +1290,7 @@
       </c>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1318,7 +1332,7 @@
       </c>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -1360,7 +1374,7 @@
       </c>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1402,7 +1416,7 @@
       </c>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -1444,7 +1458,7 @@
       </c>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -1486,7 +1500,7 @@
       </c>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -1528,7 +1542,7 @@
       </c>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -1570,7 +1584,7 @@
       </c>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -1612,7 +1626,7 @@
       </c>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -1654,7 +1668,7 @@
       </c>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -1696,7 +1710,7 @@
       </c>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1712,7 +1726,7 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1728,7 +1742,7 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1744,7 +1758,7 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1760,7 +1774,7 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1776,7 +1790,7 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1792,7 +1806,7 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1808,978 +1822,978 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2787,18 +2801,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1001"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.4921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2881,7 +2895,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2964,7 +2978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3047,7 +3061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -3130,7 +3144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -3213,7 +3227,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -3296,7 +3310,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -3379,7 +3393,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -3462,7 +3476,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -3545,7 +3559,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -3628,7 +3642,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3711,7 +3725,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -3794,7 +3808,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -3877,7 +3891,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -3960,7 +3974,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -4043,7 +4057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -4126,7 +4140,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -4209,7 +4223,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -4292,7 +4306,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -4375,7 +4389,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -4458,7 +4472,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -4541,7 +4555,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -4624,985 +4638,985 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5611,18 +5625,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1001"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.4921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5705,7 +5719,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -5788,7 +5802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -5871,7 +5885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -5954,7 +5968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -6037,7 +6051,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -6120,7 +6134,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -6203,7 +6217,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -6286,7 +6300,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -6369,7 +6383,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -6452,7 +6466,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -6535,7 +6549,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -6618,7 +6632,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -6701,7 +6715,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -6784,7 +6798,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -6867,7 +6881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -6902,7 +6916,7 @@
         <v>280000</v>
       </c>
       <c r="L16" s="3">
-        <v>0</v>
+        <v>291000</v>
       </c>
       <c r="M16" s="3">
         <v>326000</v>
@@ -6950,7 +6964,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -7033,7 +7047,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -7116,7 +7130,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -7199,7 +7213,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -7282,7 +7296,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -7365,7 +7379,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -7448,985 +7462,985 @@
         <v>319000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61C6D5B3-61FE-CE49-9B28-8AA1CECD9208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ETW\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AF64B1-1AC3-4BAA-88E0-7D4934CD5C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3684" yWindow="1800" windowWidth="22416" windowHeight="14556" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8715" yWindow="3465" windowWidth="22410" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="추가지원금" sheetId="1" r:id="rId1"/>
@@ -24,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -777,16 +780,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:N1001"/>
-  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.62890625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="12.5390625" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="16.31640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -828,7 +831,7 @@
       </c>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -870,7 +873,7 @@
       </c>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -912,7 +915,7 @@
       </c>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -954,7 +957,7 @@
       </c>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -996,7 +999,7 @@
       </c>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1038,7 +1041,7 @@
       </c>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1080,7 +1083,7 @@
       </c>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1122,7 +1125,7 @@
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1164,7 +1167,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -1206,7 +1209,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1248,7 +1251,7 @@
       </c>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1290,7 +1293,7 @@
       </c>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1332,7 +1335,7 @@
       </c>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -1374,7 +1377,7 @@
       </c>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1416,7 +1419,7 @@
       </c>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -1458,7 +1461,7 @@
       </c>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -1500,7 +1503,7 @@
       </c>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -1542,7 +1545,7 @@
       </c>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -1584,7 +1587,7 @@
       </c>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -1626,7 +1629,7 @@
       </c>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -1668,7 +1671,7 @@
       </c>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -1710,7 +1713,7 @@
       </c>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1726,7 +1729,7 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1742,7 +1745,7 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1758,7 +1761,7 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1774,7 +1777,7 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1790,7 +1793,7 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1806,7 +1809,7 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1822,978 +1825,978 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2806,13 +2809,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1001"/>
-  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.4921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2895,7 +2898,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2978,7 +2981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3061,7 +3064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -3144,7 +3147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -3227,7 +3230,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -3310,7 +3313,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -3393,7 +3396,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -3476,7 +3479,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -3559,7 +3562,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -3582,7 +3585,7 @@
         <v>228000</v>
       </c>
       <c r="H10" s="3">
-        <v>228000</v>
+        <v>233000</v>
       </c>
       <c r="I10" s="3">
         <v>237000</v>
@@ -3642,256 +3645,256 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>36000</v>
+        <v>115000</v>
       </c>
       <c r="C11" s="3">
-        <v>42000</v>
+        <v>133000</v>
       </c>
       <c r="D11" s="3">
-        <v>49000</v>
+        <v>151000</v>
       </c>
       <c r="E11" s="3">
-        <v>60000</v>
+        <v>183000</v>
       </c>
       <c r="F11" s="3">
-        <v>69000</v>
+        <v>210000</v>
       </c>
       <c r="G11" s="3">
-        <v>75000</v>
+        <v>228000</v>
       </c>
       <c r="H11" s="3">
-        <v>77000</v>
+        <v>233000</v>
       </c>
       <c r="I11" s="3">
-        <v>78000</v>
+        <v>237000</v>
       </c>
       <c r="J11" s="3">
-        <v>85000</v>
+        <v>255000</v>
       </c>
       <c r="K11" s="3">
-        <v>86000</v>
+        <v>260000</v>
       </c>
       <c r="L11" s="3">
-        <v>89000</v>
+        <v>269000</v>
       </c>
       <c r="M11" s="3">
-        <v>91000</v>
+        <v>273000</v>
       </c>
       <c r="N11" s="3">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="O11" s="3">
-        <v>107000</v>
+        <v>319000</v>
       </c>
       <c r="P11" s="3">
-        <v>111000</v>
+        <v>332000</v>
       </c>
       <c r="Q11" s="3">
-        <v>116000</v>
+        <v>346000</v>
       </c>
       <c r="R11" s="3">
-        <v>119000</v>
+        <v>355000</v>
       </c>
       <c r="S11" s="3">
-        <v>122000</v>
+        <v>364000</v>
       </c>
       <c r="T11" s="3">
-        <v>127000</v>
+        <v>377000</v>
       </c>
       <c r="U11" s="3">
-        <v>139000</v>
+        <v>413000</v>
       </c>
       <c r="V11" s="3">
-        <v>147000</v>
+        <v>450000</v>
       </c>
       <c r="W11" s="3">
-        <v>150000</v>
+        <v>500000</v>
       </c>
       <c r="X11" s="3">
-        <v>183000</v>
+        <v>500000</v>
       </c>
       <c r="Y11" s="3">
-        <v>201000</v>
+        <v>500000</v>
       </c>
       <c r="Z11" s="3">
-        <v>221000</v>
+        <v>500000</v>
       </c>
       <c r="AA11" s="3">
-        <v>250000</v>
+        <v>500000</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>36000</v>
+        <v>115000</v>
       </c>
       <c r="C12" s="3">
-        <v>42000</v>
+        <v>133000</v>
       </c>
       <c r="D12" s="3">
-        <v>49000</v>
+        <v>151000</v>
       </c>
       <c r="E12" s="3">
-        <v>60000</v>
+        <v>183000</v>
       </c>
       <c r="F12" s="3">
-        <v>69000</v>
+        <v>210000</v>
       </c>
       <c r="G12" s="3">
-        <v>75000</v>
+        <v>228000</v>
       </c>
       <c r="H12" s="3">
-        <v>77000</v>
+        <v>233000</v>
       </c>
       <c r="I12" s="3">
-        <v>78000</v>
+        <v>237000</v>
       </c>
       <c r="J12" s="3">
-        <v>85000</v>
+        <v>255000</v>
       </c>
       <c r="K12" s="3">
-        <v>86000</v>
+        <v>260000</v>
       </c>
       <c r="L12" s="3">
-        <v>89000</v>
+        <v>269000</v>
       </c>
       <c r="M12" s="3">
-        <v>91000</v>
+        <v>273000</v>
       </c>
       <c r="N12" s="3">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="O12" s="3">
-        <v>107000</v>
+        <v>319000</v>
       </c>
       <c r="P12" s="3">
-        <v>111000</v>
+        <v>332000</v>
       </c>
       <c r="Q12" s="3">
-        <v>116000</v>
+        <v>346000</v>
       </c>
       <c r="R12" s="3">
-        <v>119000</v>
+        <v>355000</v>
       </c>
       <c r="S12" s="3">
-        <v>122000</v>
+        <v>364000</v>
       </c>
       <c r="T12" s="3">
-        <v>127000</v>
+        <v>377000</v>
       </c>
       <c r="U12" s="3">
-        <v>139000</v>
+        <v>413000</v>
       </c>
       <c r="V12" s="3">
-        <v>147000</v>
+        <v>450000</v>
       </c>
       <c r="W12" s="3">
-        <v>150000</v>
+        <v>500000</v>
       </c>
       <c r="X12" s="3">
-        <v>183000</v>
+        <v>500000</v>
       </c>
       <c r="Y12" s="3">
-        <v>201000</v>
+        <v>500000</v>
       </c>
       <c r="Z12" s="3">
-        <v>221000</v>
+        <v>500000</v>
       </c>
       <c r="AA12" s="3">
-        <v>250000</v>
+        <v>500000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>36000</v>
+        <v>115000</v>
       </c>
       <c r="C13" s="3">
-        <v>42000</v>
+        <v>133000</v>
       </c>
       <c r="D13" s="3">
-        <v>49000</v>
+        <v>151000</v>
       </c>
       <c r="E13" s="3">
-        <v>60000</v>
+        <v>183000</v>
       </c>
       <c r="F13" s="3">
-        <v>69000</v>
+        <v>210000</v>
       </c>
       <c r="G13" s="3">
-        <v>75000</v>
+        <v>228000</v>
       </c>
       <c r="H13" s="3">
-        <v>77000</v>
+        <v>233000</v>
       </c>
       <c r="I13" s="3">
-        <v>78000</v>
+        <v>237000</v>
       </c>
       <c r="J13" s="3">
-        <v>85000</v>
+        <v>255000</v>
       </c>
       <c r="K13" s="3">
-        <v>86000</v>
+        <v>260000</v>
       </c>
       <c r="L13" s="3">
-        <v>89000</v>
+        <v>269000</v>
       </c>
       <c r="M13" s="3">
-        <v>91000</v>
+        <v>273000</v>
       </c>
       <c r="N13" s="3">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="O13" s="3">
-        <v>107000</v>
+        <v>319000</v>
       </c>
       <c r="P13" s="3">
-        <v>111000</v>
+        <v>332000</v>
       </c>
       <c r="Q13" s="3">
-        <v>116000</v>
+        <v>346000</v>
       </c>
       <c r="R13" s="3">
-        <v>119000</v>
+        <v>355000</v>
       </c>
       <c r="S13" s="3">
-        <v>122000</v>
+        <v>364000</v>
       </c>
       <c r="T13" s="3">
-        <v>127000</v>
+        <v>377000</v>
       </c>
       <c r="U13" s="3">
-        <v>139000</v>
+        <v>413000</v>
       </c>
       <c r="V13" s="3">
-        <v>147000</v>
+        <v>450000</v>
       </c>
       <c r="W13" s="3">
-        <v>150000</v>
+        <v>500000</v>
       </c>
       <c r="X13" s="3">
-        <v>183000</v>
+        <v>500000</v>
       </c>
       <c r="Y13" s="3">
-        <v>201000</v>
+        <v>500000</v>
       </c>
       <c r="Z13" s="3">
-        <v>221000</v>
+        <v>500000</v>
       </c>
       <c r="AA13" s="3">
-        <v>250000</v>
+        <v>500000</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -3974,7 +3977,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -4057,7 +4060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -4140,7 +4143,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -4223,7 +4226,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -4306,7 +4309,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -4389,7 +4392,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -4472,7 +4475,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -4555,7 +4558,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -4638,985 +4641,985 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5630,13 +5633,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1001"/>
-  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.4921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -5719,7 +5722,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -5802,7 +5805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -5885,7 +5888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -5968,7 +5971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -6051,7 +6054,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -6134,7 +6137,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -6217,7 +6220,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -6300,7 +6303,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -6383,7 +6386,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -6466,7 +6469,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -6477,79 +6480,79 @@
         <v>0</v>
       </c>
       <c r="D11" s="3">
-        <v>52000</v>
+        <v>175000</v>
       </c>
       <c r="E11" s="3">
-        <v>59000</v>
+        <v>198000</v>
       </c>
       <c r="F11" s="3">
-        <v>66000</v>
+        <v>222000</v>
       </c>
       <c r="G11" s="3">
-        <v>69000</v>
+        <v>233000</v>
       </c>
       <c r="H11" s="3">
-        <v>76000</v>
+        <v>257000</v>
       </c>
       <c r="I11" s="3">
-        <v>78000</v>
+        <v>262000</v>
       </c>
       <c r="J11" s="3">
-        <v>80000</v>
+        <v>268000</v>
       </c>
       <c r="K11" s="3">
-        <v>84000</v>
+        <v>280000</v>
       </c>
       <c r="L11" s="3">
-        <v>87000</v>
+        <v>291000</v>
       </c>
       <c r="M11" s="3">
-        <v>98000</v>
+        <v>326000</v>
       </c>
       <c r="N11" s="3">
-        <v>105000</v>
+        <v>350000</v>
       </c>
       <c r="O11" s="3">
-        <v>108000</v>
+        <v>361000</v>
       </c>
       <c r="P11" s="3">
-        <v>112000</v>
+        <v>373000</v>
       </c>
       <c r="Q11" s="3">
-        <v>117000</v>
+        <v>390000</v>
       </c>
       <c r="R11" s="3">
-        <v>121000</v>
+        <v>402000</v>
       </c>
       <c r="S11" s="3">
-        <v>122000</v>
+        <v>407000</v>
       </c>
       <c r="T11" s="3">
-        <v>124000</v>
+        <v>414000</v>
       </c>
       <c r="U11" s="3">
-        <v>133000</v>
+        <v>442000</v>
       </c>
       <c r="V11" s="3">
-        <v>138000</v>
+        <v>460000</v>
       </c>
       <c r="W11" s="3">
-        <v>151000</v>
+        <v>500000</v>
       </c>
       <c r="X11" s="3">
-        <v>168000</v>
+        <v>500000</v>
       </c>
       <c r="Y11" s="3">
-        <v>186000</v>
+        <v>500000</v>
       </c>
       <c r="Z11" s="3">
-        <v>204000</v>
+        <v>500000</v>
       </c>
       <c r="AA11" s="3">
-        <v>230000</v>
+        <v>500000</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -6560,79 +6563,79 @@
         <v>0</v>
       </c>
       <c r="D12" s="3">
-        <v>52000</v>
+        <v>175000</v>
       </c>
       <c r="E12" s="3">
-        <v>59000</v>
+        <v>198000</v>
       </c>
       <c r="F12" s="3">
-        <v>66000</v>
+        <v>222000</v>
       </c>
       <c r="G12" s="3">
-        <v>69000</v>
+        <v>233000</v>
       </c>
       <c r="H12" s="3">
-        <v>76000</v>
+        <v>257000</v>
       </c>
       <c r="I12" s="3">
-        <v>78000</v>
+        <v>262000</v>
       </c>
       <c r="J12" s="3">
-        <v>80000</v>
+        <v>268000</v>
       </c>
       <c r="K12" s="3">
-        <v>84000</v>
+        <v>280000</v>
       </c>
       <c r="L12" s="3">
-        <v>87000</v>
+        <v>291000</v>
       </c>
       <c r="M12" s="3">
-        <v>98000</v>
+        <v>326000</v>
       </c>
       <c r="N12" s="3">
-        <v>105000</v>
+        <v>350000</v>
       </c>
       <c r="O12" s="3">
-        <v>108000</v>
+        <v>361000</v>
       </c>
       <c r="P12" s="3">
-        <v>112000</v>
+        <v>373000</v>
       </c>
       <c r="Q12" s="3">
-        <v>117000</v>
+        <v>390000</v>
       </c>
       <c r="R12" s="3">
-        <v>121000</v>
+        <v>402000</v>
       </c>
       <c r="S12" s="3">
-        <v>122000</v>
+        <v>407000</v>
       </c>
       <c r="T12" s="3">
-        <v>124000</v>
+        <v>414000</v>
       </c>
       <c r="U12" s="3">
-        <v>133000</v>
+        <v>442000</v>
       </c>
       <c r="V12" s="3">
-        <v>138000</v>
+        <v>460000</v>
       </c>
       <c r="W12" s="3">
-        <v>151000</v>
+        <v>500000</v>
       </c>
       <c r="X12" s="3">
-        <v>168000</v>
+        <v>500000</v>
       </c>
       <c r="Y12" s="3">
-        <v>186000</v>
+        <v>500000</v>
       </c>
       <c r="Z12" s="3">
-        <v>204000</v>
+        <v>500000</v>
       </c>
       <c r="AA12" s="3">
-        <v>230000</v>
+        <v>500000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -6643,79 +6646,79 @@
         <v>0</v>
       </c>
       <c r="D13" s="3">
-        <v>52000</v>
+        <v>175000</v>
       </c>
       <c r="E13" s="3">
-        <v>59000</v>
+        <v>198000</v>
       </c>
       <c r="F13" s="3">
-        <v>66000</v>
+        <v>222000</v>
       </c>
       <c r="G13" s="3">
-        <v>69000</v>
+        <v>233000</v>
       </c>
       <c r="H13" s="3">
-        <v>76000</v>
+        <v>257000</v>
       </c>
       <c r="I13" s="3">
-        <v>78000</v>
+        <v>262000</v>
       </c>
       <c r="J13" s="3">
-        <v>80000</v>
+        <v>268000</v>
       </c>
       <c r="K13" s="3">
-        <v>84000</v>
+        <v>280000</v>
       </c>
       <c r="L13" s="3">
-        <v>87000</v>
+        <v>291000</v>
       </c>
       <c r="M13" s="3">
-        <v>98000</v>
+        <v>326000</v>
       </c>
       <c r="N13" s="3">
-        <v>105000</v>
+        <v>350000</v>
       </c>
       <c r="O13" s="3">
-        <v>108000</v>
+        <v>361000</v>
       </c>
       <c r="P13" s="3">
-        <v>112000</v>
+        <v>373000</v>
       </c>
       <c r="Q13" s="3">
-        <v>117000</v>
+        <v>390000</v>
       </c>
       <c r="R13" s="3">
-        <v>121000</v>
+        <v>402000</v>
       </c>
       <c r="S13" s="3">
-        <v>122000</v>
+        <v>407000</v>
       </c>
       <c r="T13" s="3">
-        <v>124000</v>
+        <v>414000</v>
       </c>
       <c r="U13" s="3">
-        <v>133000</v>
+        <v>442000</v>
       </c>
       <c r="V13" s="3">
-        <v>138000</v>
+        <v>460000</v>
       </c>
       <c r="W13" s="3">
-        <v>151000</v>
+        <v>500000</v>
       </c>
       <c r="X13" s="3">
-        <v>168000</v>
+        <v>500000</v>
       </c>
       <c r="Y13" s="3">
-        <v>186000</v>
+        <v>500000</v>
       </c>
       <c r="Z13" s="3">
-        <v>204000</v>
+        <v>500000</v>
       </c>
       <c r="AA13" s="3">
-        <v>230000</v>
+        <v>500000</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -6798,7 +6801,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -6881,7 +6884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -6964,7 +6967,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -7047,7 +7050,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -7130,7 +7133,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -7213,7 +7216,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -7296,7 +7299,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -7379,7 +7382,7 @@
         <v>230000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -7462,985 +7465,985 @@
         <v>319000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/policy.xlsx
+++ b/policy.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ETW\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76AF64B1-1AC3-4BAA-88E0-7D4934CD5C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8715" yWindow="3465" windowWidth="22410" windowHeight="14550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8712" yWindow="3468" windowWidth="22416" windowHeight="14556"/>
   </bookViews>
   <sheets>
     <sheet name="추가지원금" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">추가지원금!$A$1:$M$22</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -497,7 +491,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -775,21 +769,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:N1001"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -831,7 +825,7 @@
       </c>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -873,7 +867,7 @@
       </c>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -915,7 +909,7 @@
       </c>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -957,7 +951,7 @@
       </c>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -974,32 +968,32 @@
         <v>460000</v>
       </c>
       <c r="F5" s="2">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="G5" s="2">
         <v>30000</v>
       </c>
       <c r="H5" s="2">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="I5" s="2">
         <v>30000</v>
       </c>
       <c r="J5" s="2">
-        <v>450000</v>
+        <v>350000</v>
       </c>
       <c r="K5" s="2">
         <v>50000</v>
       </c>
       <c r="L5" s="2">
-        <v>450000</v>
+        <v>350000</v>
       </c>
       <c r="M5" s="2">
         <v>50000</v>
       </c>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1041,7 +1035,7 @@
       </c>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1083,7 +1077,7 @@
       </c>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1100,32 +1094,32 @@
         <v>360000</v>
       </c>
       <c r="F8" s="2">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="G8" s="2">
         <v>30000</v>
       </c>
       <c r="H8" s="2">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="I8" s="2">
         <v>30000</v>
       </c>
       <c r="J8" s="2">
-        <v>450000</v>
+        <v>350000</v>
       </c>
       <c r="K8" s="2">
         <v>50000</v>
       </c>
       <c r="L8" s="2">
-        <v>450000</v>
+        <v>350000</v>
       </c>
       <c r="M8" s="2">
         <v>50000</v>
       </c>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1167,7 +1161,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -1209,7 +1203,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1226,32 +1220,32 @@
         <v>500000</v>
       </c>
       <c r="F11" s="2">
-        <v>280000</v>
+        <v>200000</v>
       </c>
       <c r="G11" s="2">
         <v>30000</v>
       </c>
       <c r="H11" s="2">
-        <v>280000</v>
+        <v>200000</v>
       </c>
       <c r="I11" s="2">
         <v>30000</v>
       </c>
       <c r="J11" s="2">
-        <v>330000</v>
+        <v>250000</v>
       </c>
       <c r="K11" s="2">
         <v>50000</v>
       </c>
       <c r="L11" s="2">
-        <v>330000</v>
+        <v>250000</v>
       </c>
       <c r="M11" s="2">
         <v>50000</v>
       </c>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1268,32 +1262,32 @@
         <v>0</v>
       </c>
       <c r="F12" s="2">
-        <v>280000</v>
+        <v>200000</v>
       </c>
       <c r="G12" s="2">
         <v>30000</v>
       </c>
       <c r="H12" s="2">
-        <v>280000</v>
+        <v>200000</v>
       </c>
       <c r="I12" s="2">
         <v>30000</v>
       </c>
       <c r="J12" s="2">
-        <v>330000</v>
+        <v>250000</v>
       </c>
       <c r="K12" s="2">
         <v>50000</v>
       </c>
       <c r="L12" s="2">
-        <v>330000</v>
+        <v>250000</v>
       </c>
       <c r="M12" s="2">
         <v>50000</v>
       </c>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1310,32 +1304,32 @@
         <v>500000</v>
       </c>
       <c r="F13" s="2">
-        <v>280000</v>
+        <v>200000</v>
       </c>
       <c r="G13" s="2">
         <v>30000</v>
       </c>
       <c r="H13" s="2">
-        <v>280000</v>
+        <v>200000</v>
       </c>
       <c r="I13" s="2">
         <v>30000</v>
       </c>
       <c r="J13" s="2">
-        <v>330000</v>
+        <v>250000</v>
       </c>
       <c r="K13" s="2">
         <v>50000</v>
       </c>
       <c r="L13" s="2">
-        <v>330000</v>
+        <v>250000</v>
       </c>
       <c r="M13" s="2">
         <v>50000</v>
       </c>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -1352,32 +1346,32 @@
         <v>500000</v>
       </c>
       <c r="F14" s="2">
-        <v>280000</v>
+        <v>200000</v>
       </c>
       <c r="G14" s="2">
         <v>30000</v>
       </c>
       <c r="H14" s="2">
-        <v>280000</v>
+        <v>200000</v>
       </c>
       <c r="I14" s="2">
         <v>30000</v>
       </c>
       <c r="J14" s="2">
-        <v>330000</v>
+        <v>250000</v>
       </c>
       <c r="K14" s="2">
         <v>50000</v>
       </c>
       <c r="L14" s="2">
-        <v>330000</v>
+        <v>250000</v>
       </c>
       <c r="M14" s="2">
         <v>50000</v>
       </c>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -1419,7 +1413,7 @@
       </c>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -1461,7 +1455,7 @@
       </c>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -1484,7 +1478,7 @@
         <v>30000</v>
       </c>
       <c r="H17" s="2">
-        <v>250000</v>
+        <v>400000</v>
       </c>
       <c r="I17" s="2">
         <v>30000</v>
@@ -1496,14 +1490,14 @@
         <v>50000</v>
       </c>
       <c r="L17" s="2">
-        <v>300000</v>
+        <v>450000</v>
       </c>
       <c r="M17" s="2">
         <v>50000</v>
       </c>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -1526,7 +1520,7 @@
         <v>30000</v>
       </c>
       <c r="H18" s="2">
-        <v>250000</v>
+        <v>400000</v>
       </c>
       <c r="I18" s="2">
         <v>30000</v>
@@ -1538,14 +1532,14 @@
         <v>50000</v>
       </c>
       <c r="L18" s="2">
-        <v>300000</v>
+        <v>450000</v>
       </c>
       <c r="M18" s="2">
         <v>50000</v>
       </c>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -1587,7 +1581,7 @@
       </c>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -1629,7 +1623,7 @@
       </c>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -1671,7 +1665,7 @@
       </c>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -1713,7 +1707,7 @@
       </c>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1729,7 +1723,7 @@
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1745,7 +1739,7 @@
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1761,7 +1755,7 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1777,7 +1771,7 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1793,7 +1787,7 @@
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1809,7 +1803,7 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1825,978 +1819,978 @@
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2804,18 +2798,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AA1001"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="27" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="8.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2898,7 +2892,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2981,7 +2975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3064,7 +3058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -3147,7 +3141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -3230,7 +3224,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -3313,7 +3307,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -3396,7 +3390,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -3479,7 +3473,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -3562,7 +3556,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -3645,7 +3639,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -3728,7 +3722,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -3811,7 +3805,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -3894,7 +3888,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -3977,7 +3971,7 @@
         <v>700000</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -4060,7 +4054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -4143,7 +4137,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -4226,7 +4220,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -4309,7 +4303,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -4392,7 +4386,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -4475,7 +4469,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -4558,7 +4552,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -4641,985 +4635,985 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14a